--- a/research/traditional_assets/database/data/luxembourg/luxembourg_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_drugs_pharmaceutical.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08408258263289962</v>
+        <v>0.08390665767181317</v>
       </c>
       <c r="C2">
-        <v>478.844336923531</v>
+        <v>475.1262470434822</v>
       </c>
       <c r="D2">
-        <v>461.244336923531</v>
+        <v>463.0652470434822</v>
       </c>
       <c r="E2">
-        <v>-289.9</v>
+        <v>-284.361</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.539</v>
       </c>
       <c r="G2">
         <v>17.6</v>
@@ -1439,28 +1439,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2786117</v>
       </c>
       <c r="N2">
-        <v>86.76666666666668</v>
+        <v>86.48805496666668</v>
       </c>
       <c r="O2">
-        <v>21.63960666666667</v>
+        <v>21.57012090868667</v>
       </c>
       <c r="P2">
-        <v>65.12706</v>
+        <v>64.91793405798001</v>
       </c>
       <c r="Q2">
-        <v>73.52706000000001</v>
+        <v>73.31793405798001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08408258263289962</v>
+        <v>0.0843728342139527</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8908275799989077</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>311.4250645851079</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08390665767181317</v>
+        <v>0.08373073271072673</v>
       </c>
       <c r="C3">
-        <v>475.1262470434822</v>
+        <v>471.4225914019657</v>
       </c>
       <c r="D3">
-        <v>463.0652470434822</v>
+        <v>464.9005914019657</v>
       </c>
       <c r="E3">
-        <v>-284.361</v>
+        <v>-278.822</v>
       </c>
       <c r="F3">
-        <v>5.539</v>
+        <v>11.078</v>
       </c>
       <c r="G3">
         <v>17.6</v>
@@ -1521,28 +1521,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M3">
-        <v>0.2786117</v>
+        <v>0.5572233999999999</v>
       </c>
       <c r="N3">
-        <v>86.48805496666668</v>
+        <v>86.20944326666668</v>
       </c>
       <c r="O3">
-        <v>21.57012090868667</v>
+        <v>21.50063515070667</v>
       </c>
       <c r="P3">
-        <v>64.91793405798001</v>
+        <v>64.70880811596001</v>
       </c>
       <c r="Q3">
-        <v>73.31793405798001</v>
+        <v>73.10880811596002</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0843728342139527</v>
+        <v>0.08466900929665992</v>
       </c>
       <c r="T3">
-        <v>0.8908275799989077</v>
+        <v>0.8976676511930699</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>311.4250645851079</v>
+        <v>155.7125322925539</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08373073271072673</v>
+        <v>0.08355480774964028</v>
       </c>
       <c r="C4">
-        <v>471.4225914019657</v>
+        <v>467.7335423108686</v>
       </c>
       <c r="D4">
-        <v>464.9005914019657</v>
+        <v>466.7505423108686</v>
       </c>
       <c r="E4">
-        <v>-278.822</v>
+        <v>-273.283</v>
       </c>
       <c r="F4">
-        <v>11.078</v>
+        <v>16.617</v>
       </c>
       <c r="G4">
         <v>17.6</v>
@@ -1603,28 +1603,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M4">
-        <v>0.5572233999999999</v>
+        <v>0.8358350999999998</v>
       </c>
       <c r="N4">
-        <v>86.20944326666668</v>
+        <v>85.93083156666668</v>
       </c>
       <c r="O4">
-        <v>21.50063515070667</v>
+        <v>21.43114939272667</v>
       </c>
       <c r="P4">
-        <v>64.70880811596001</v>
+        <v>64.49968217394002</v>
       </c>
       <c r="Q4">
-        <v>73.10880811596002</v>
+        <v>72.89968217394002</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08466900929665992</v>
+        <v>0.08497129108210337</v>
       </c>
       <c r="T4">
-        <v>0.8976676511930699</v>
+        <v>0.9046487547829879</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.7125322925539</v>
+        <v>103.8083548617026</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08355480774964028</v>
+        <v>0.08337888278855381</v>
       </c>
       <c r="C5">
-        <v>467.7335423108686</v>
+        <v>464.0592748357164</v>
       </c>
       <c r="D5">
-        <v>466.7505423108686</v>
+        <v>468.6152748357164</v>
       </c>
       <c r="E5">
-        <v>-273.283</v>
+        <v>-267.744</v>
       </c>
       <c r="F5">
-        <v>16.617</v>
+        <v>22.156</v>
       </c>
       <c r="G5">
         <v>17.6</v>
@@ -1685,28 +1685,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M5">
-        <v>0.8358350999999998</v>
+        <v>1.1144468</v>
       </c>
       <c r="N5">
-        <v>85.93083156666668</v>
+        <v>85.65221986666668</v>
       </c>
       <c r="O5">
-        <v>21.43114939272667</v>
+        <v>21.36166363474667</v>
       </c>
       <c r="P5">
-        <v>64.49968217394002</v>
+        <v>64.29055623192001</v>
       </c>
       <c r="Q5">
-        <v>72.89968217394002</v>
+        <v>72.69055623192</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08497129108210337</v>
+        <v>0.08527987040474355</v>
       </c>
       <c r="T5">
-        <v>0.9046487547829879</v>
+        <v>0.9117752980310292</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.8083548617026</v>
+        <v>77.85626614627697</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08337888278855381</v>
+        <v>0.08320295782746737</v>
       </c>
       <c r="C6">
-        <v>464.0592748357164</v>
+        <v>460.399966850899</v>
       </c>
       <c r="D6">
-        <v>468.6152748357164</v>
+        <v>470.4949668508989</v>
       </c>
       <c r="E6">
-        <v>-267.744</v>
+        <v>-262.205</v>
       </c>
       <c r="F6">
-        <v>22.156</v>
+        <v>27.695</v>
       </c>
       <c r="G6">
         <v>17.6</v>
@@ -1767,28 +1767,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M6">
-        <v>1.1144468</v>
+        <v>1.3930585</v>
       </c>
       <c r="N6">
-        <v>85.65221986666668</v>
+        <v>85.37360816666668</v>
       </c>
       <c r="O6">
-        <v>21.36166363474667</v>
+        <v>21.29217787676667</v>
       </c>
       <c r="P6">
-        <v>64.29055623192001</v>
+        <v>64.08143028990001</v>
       </c>
       <c r="Q6">
-        <v>72.69055623192</v>
+        <v>72.4814302899</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08527987040474355</v>
+        <v>0.08559494613417618</v>
       </c>
       <c r="T6">
-        <v>0.9117752980310292</v>
+        <v>0.9190518737685031</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.85626614627697</v>
+        <v>62.28501291702157</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08320295782746737</v>
+        <v>0.08302703286638091</v>
       </c>
       <c r="C7">
-        <v>460.399966850899</v>
+        <v>456.7557990962334</v>
       </c>
       <c r="D7">
-        <v>470.4949668508989</v>
+        <v>472.3897990962333</v>
       </c>
       <c r="E7">
-        <v>-262.205</v>
+        <v>-256.666</v>
       </c>
       <c r="F7">
-        <v>27.695</v>
+        <v>33.234</v>
       </c>
       <c r="G7">
         <v>17.6</v>
@@ -1849,28 +1849,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M7">
-        <v>1.3930585</v>
+        <v>1.6716702</v>
       </c>
       <c r="N7">
-        <v>85.37360816666668</v>
+        <v>85.09499646666669</v>
       </c>
       <c r="O7">
-        <v>21.29217787676667</v>
+        <v>21.22269211878667</v>
       </c>
       <c r="P7">
-        <v>64.08143028990001</v>
+        <v>63.87230434788002</v>
       </c>
       <c r="Q7">
-        <v>72.4814302899</v>
+        <v>72.27230434788001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08559494613417618</v>
+        <v>0.08591672560253288</v>
       </c>
       <c r="T7">
-        <v>0.9190518737685031</v>
+        <v>0.9264832702663486</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.28501291702157</v>
+        <v>51.9041774308513</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08302703286638091</v>
+        <v>0.08285110790529449</v>
       </c>
       <c r="C8">
-        <v>456.7557990962334</v>
+        <v>453.1269552348949</v>
       </c>
       <c r="D8">
-        <v>472.3897990962333</v>
+        <v>474.2999552348949</v>
       </c>
       <c r="E8">
-        <v>-256.666</v>
+        <v>-251.127</v>
       </c>
       <c r="F8">
-        <v>33.23399999999999</v>
+        <v>38.773</v>
       </c>
       <c r="G8">
         <v>17.6</v>
@@ -1931,28 +1931,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M8">
-        <v>1.6716702</v>
+        <v>1.9502819</v>
       </c>
       <c r="N8">
-        <v>85.09499646666669</v>
+        <v>84.81638476666669</v>
       </c>
       <c r="O8">
-        <v>21.22269211878667</v>
+        <v>21.15320636080667</v>
       </c>
       <c r="P8">
-        <v>63.87230434788002</v>
+        <v>63.66317840586001</v>
       </c>
       <c r="Q8">
-        <v>72.27230434788001</v>
+        <v>72.06317840586001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08591672560253288</v>
+        <v>0.08624542505945643</v>
       </c>
       <c r="T8">
-        <v>0.9264832702663486</v>
+        <v>0.9340744817426426</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.90417743085131</v>
+        <v>44.48929494072969</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08285110790529447</v>
+        <v>0.08267518294420802</v>
       </c>
       <c r="C9">
-        <v>453.1269552348951</v>
+        <v>449.5136219127638</v>
       </c>
       <c r="D9">
-        <v>474.2999552348951</v>
+        <v>476.2256219127638</v>
       </c>
       <c r="E9">
-        <v>-251.127</v>
+        <v>-245.588</v>
       </c>
       <c r="F9">
-        <v>38.773</v>
+        <v>44.312</v>
       </c>
       <c r="G9">
         <v>17.6</v>
@@ -2013,28 +2013,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M9">
-        <v>1.9502819</v>
+        <v>2.2288936</v>
       </c>
       <c r="N9">
-        <v>84.81638476666669</v>
+        <v>84.53777306666667</v>
       </c>
       <c r="O9">
-        <v>21.15320636080667</v>
+        <v>21.08372060282667</v>
       </c>
       <c r="P9">
-        <v>63.66317840586001</v>
+        <v>63.45405246384</v>
       </c>
       <c r="Q9">
-        <v>72.06317840586001</v>
+        <v>71.85405246383999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08624542505945643</v>
+        <v>0.08658127015674784</v>
       </c>
       <c r="T9">
-        <v>0.9340744817426426</v>
+        <v>0.9418307195553776</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.48929494072969</v>
+        <v>38.92813307313848</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08267518294420802</v>
+        <v>0.08249925798312156</v>
       </c>
       <c r="C10">
-        <v>449.5136219127638</v>
+        <v>445.9159888192186</v>
       </c>
       <c r="D10">
-        <v>476.2256219127638</v>
+        <v>478.1669888192186</v>
       </c>
       <c r="E10">
-        <v>-245.588</v>
+        <v>-240.049</v>
       </c>
       <c r="F10">
-        <v>44.312</v>
+        <v>49.851</v>
       </c>
       <c r="G10">
         <v>17.6</v>
@@ -2095,28 +2095,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M10">
-        <v>2.2288936</v>
+        <v>2.5075053</v>
       </c>
       <c r="N10">
-        <v>84.53777306666667</v>
+        <v>84.25916136666667</v>
       </c>
       <c r="O10">
-        <v>21.08372060282667</v>
+        <v>21.01423484484667</v>
       </c>
       <c r="P10">
-        <v>63.45405246384</v>
+        <v>63.24492652182001</v>
       </c>
       <c r="Q10">
-        <v>71.85405246383999</v>
+        <v>71.64492652182</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08658127015674784</v>
+        <v>0.08692449646496875</v>
       </c>
       <c r="T10">
-        <v>0.9418307195553776</v>
+        <v>0.9497574241332276</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.92813307313848</v>
+        <v>34.60278495390087</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08249925798312156</v>
+        <v>0.08232333302203511</v>
       </c>
       <c r="C11">
-        <v>445.9159888192186</v>
+        <v>442.3342487494274</v>
       </c>
       <c r="D11">
-        <v>478.1669888192186</v>
+        <v>480.1242487494274</v>
       </c>
       <c r="E11">
-        <v>-240.049</v>
+        <v>-234.51</v>
       </c>
       <c r="F11">
-        <v>49.851</v>
+        <v>55.38999999999999</v>
       </c>
       <c r="G11">
         <v>17.6</v>
@@ -2177,28 +2177,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M11">
-        <v>2.5075053</v>
+        <v>2.786117</v>
       </c>
       <c r="N11">
-        <v>84.25916136666667</v>
+        <v>83.98054966666668</v>
       </c>
       <c r="O11">
-        <v>21.01423484484667</v>
+        <v>20.94474908686667</v>
       </c>
       <c r="P11">
-        <v>63.24492652182001</v>
+        <v>63.03580057980001</v>
       </c>
       <c r="Q11">
-        <v>71.64492652182</v>
+        <v>71.4358005798</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08692449646496875</v>
+        <v>0.08727535002448344</v>
       </c>
       <c r="T11">
-        <v>0.9497574241332276</v>
+        <v>0.9578602777016965</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.60278495390087</v>
+        <v>31.14250645851078</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08232333302203511</v>
+        <v>0.08214740806094867</v>
       </c>
       <c r="C12">
-        <v>442.3342487494274</v>
+        <v>438.7685976681719</v>
       </c>
       <c r="D12">
-        <v>480.1242487494274</v>
+        <v>482.0975976681719</v>
       </c>
       <c r="E12">
-        <v>-234.51</v>
+        <v>-228.971</v>
       </c>
       <c r="F12">
-        <v>55.39</v>
+        <v>60.92899999999999</v>
       </c>
       <c r="G12">
         <v>17.6</v>
@@ -2259,28 +2259,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M12">
-        <v>2.786117</v>
+        <v>3.064728699999999</v>
       </c>
       <c r="N12">
-        <v>83.98054966666668</v>
+        <v>83.70193796666668</v>
       </c>
       <c r="O12">
-        <v>20.94474908686667</v>
+        <v>20.87526332888667</v>
       </c>
       <c r="P12">
-        <v>63.03580057980001</v>
+        <v>62.82667463778</v>
       </c>
       <c r="Q12">
-        <v>71.4358005798</v>
+        <v>71.22667463778001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08727535002448344</v>
+        <v>0.08763408793365018</v>
       </c>
       <c r="T12">
-        <v>0.9578602777016965</v>
+        <v>0.9661452178672097</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.14250645851078</v>
+        <v>28.31136950773708</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08214740806094867</v>
+        <v>0.0819714830998622</v>
       </c>
       <c r="C13">
-        <v>438.7685976681719</v>
+        <v>435.2192347752543</v>
       </c>
       <c r="D13">
-        <v>482.0975976681719</v>
+        <v>484.0872347752543</v>
       </c>
       <c r="E13">
-        <v>-228.971</v>
+        <v>-223.432</v>
       </c>
       <c r="F13">
-        <v>60.92899999999999</v>
+        <v>66.46799999999999</v>
       </c>
       <c r="G13">
         <v>17.6</v>
@@ -2341,28 +2341,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M13">
-        <v>3.064728699999999</v>
+        <v>3.343340399999999</v>
       </c>
       <c r="N13">
-        <v>83.70193796666668</v>
+        <v>83.42332626666668</v>
       </c>
       <c r="O13">
-        <v>20.87526332888667</v>
+        <v>20.80577757090667</v>
       </c>
       <c r="P13">
-        <v>62.82667463778</v>
+        <v>62.61754869576001</v>
       </c>
       <c r="Q13">
-        <v>71.22667463778001</v>
+        <v>71.01754869576001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08763408793365018</v>
+        <v>0.08800097897711615</v>
       </c>
       <c r="T13">
-        <v>0.9661452178672097</v>
+        <v>0.9746184521273937</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.31136950773708</v>
+        <v>25.95208871542566</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0819714830998622</v>
+        <v>0.08179555813877575</v>
       </c>
       <c r="C14">
-        <v>435.2192347752543</v>
+        <v>431.6863625725274</v>
       </c>
       <c r="D14">
-        <v>484.0872347752543</v>
+        <v>486.0933625725274</v>
       </c>
       <c r="E14">
-        <v>-223.432</v>
+        <v>-217.893</v>
       </c>
       <c r="F14">
-        <v>66.46799999999999</v>
+        <v>72.00700000000001</v>
       </c>
       <c r="G14">
         <v>17.6</v>
@@ -2423,28 +2423,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M14">
-        <v>3.343340399999999</v>
+        <v>3.6219521</v>
       </c>
       <c r="N14">
-        <v>83.42332626666668</v>
+        <v>83.14471456666668</v>
       </c>
       <c r="O14">
-        <v>20.80577757090667</v>
+        <v>20.73629181292667</v>
       </c>
       <c r="P14">
-        <v>62.61754869576001</v>
+        <v>62.40842275374001</v>
       </c>
       <c r="Q14">
-        <v>71.01754869576001</v>
+        <v>70.80842275374002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08800097897711615</v>
+        <v>0.08837630429744339</v>
       </c>
       <c r="T14">
-        <v>0.9746184521273937</v>
+        <v>0.9832864733820648</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.95208871542566</v>
+        <v>23.95577419885445</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08179555813877575</v>
+        <v>0.0816196331776893</v>
       </c>
       <c r="C15">
-        <v>431.6863625725274</v>
+        <v>428.1701869326017</v>
       </c>
       <c r="D15">
-        <v>486.0933625725274</v>
+        <v>488.1161869326017</v>
       </c>
       <c r="E15">
-        <v>-217.893</v>
+        <v>-212.354</v>
       </c>
       <c r="F15">
-        <v>72.00700000000001</v>
+        <v>77.54600000000001</v>
       </c>
       <c r="G15">
         <v>17.6</v>
@@ -2505,28 +2505,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M15">
-        <v>3.6219521</v>
+        <v>3.9005638</v>
       </c>
       <c r="N15">
-        <v>83.14471456666668</v>
+        <v>82.86610286666668</v>
       </c>
       <c r="O15">
-        <v>20.73629181292667</v>
+        <v>20.66680605494667</v>
       </c>
       <c r="P15">
-        <v>62.40842275374001</v>
+        <v>62.19929681172</v>
       </c>
       <c r="Q15">
-        <v>70.80842275374002</v>
+        <v>70.59929681172</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08837630429744339</v>
+        <v>0.08876035811359222</v>
       </c>
       <c r="T15">
-        <v>0.9832864733820648</v>
+        <v>0.9921560765263793</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.95577419885445</v>
+        <v>22.24464747036484</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0816196331776893</v>
+        <v>0.08144370821660284</v>
       </c>
       <c r="C16">
-        <v>428.1701869326017</v>
+        <v>424.6709171692736</v>
       </c>
       <c r="D16">
-        <v>488.1161869326017</v>
+        <v>490.1559171692736</v>
       </c>
       <c r="E16">
-        <v>-212.354</v>
+        <v>-206.815</v>
       </c>
       <c r="F16">
-        <v>77.54600000000001</v>
+        <v>83.08500000000001</v>
       </c>
       <c r="G16">
         <v>17.6</v>
@@ -2587,28 +2587,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M16">
-        <v>3.9005638</v>
+        <v>4.1791755</v>
       </c>
       <c r="N16">
-        <v>82.86610286666668</v>
+        <v>82.58749116666668</v>
       </c>
       <c r="O16">
-        <v>20.66680605494667</v>
+        <v>20.59732029696667</v>
       </c>
       <c r="P16">
-        <v>62.19929681172</v>
+        <v>61.99017086970001</v>
       </c>
       <c r="Q16">
-        <v>70.59929681172</v>
+        <v>70.3901708697</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08876035811359222</v>
+        <v>0.089153448490121</v>
       </c>
       <c r="T16">
-        <v>0.9921560765263793</v>
+        <v>1.001234376215266</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.24464747036484</v>
+        <v>20.76167097234052</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08144370821660284</v>
+        <v>0.08126778325551638</v>
       </c>
       <c r="C17">
-        <v>424.6709171692736</v>
+        <v>421.1887661097256</v>
       </c>
       <c r="D17">
-        <v>490.1559171692736</v>
+        <v>492.2127661097256</v>
       </c>
       <c r="E17">
-        <v>-206.815</v>
+        <v>-201.276</v>
       </c>
       <c r="F17">
-        <v>83.08499999999999</v>
+        <v>88.624</v>
       </c>
       <c r="G17">
         <v>17.6</v>
@@ -2669,28 +2669,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M17">
-        <v>4.179175499999999</v>
+        <v>4.457787199999999</v>
       </c>
       <c r="N17">
-        <v>82.58749116666668</v>
+        <v>82.30887946666668</v>
       </c>
       <c r="O17">
-        <v>20.59732029696667</v>
+        <v>20.52783453898667</v>
       </c>
       <c r="P17">
-        <v>61.99017086970001</v>
+        <v>61.78104492768001</v>
       </c>
       <c r="Q17">
-        <v>70.3901708697</v>
+        <v>70.18104492768001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.089153448490121</v>
+        <v>0.08955589816132904</v>
       </c>
       <c r="T17">
-        <v>1.001234376215266</v>
+        <v>1.010528825896745</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.76167097234052</v>
+        <v>19.46406653656924</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08126778325551638</v>
+        <v>0.08109185829442993</v>
       </c>
       <c r="C18">
-        <v>421.1887661097256</v>
+        <v>417.7239501685552</v>
       </c>
       <c r="D18">
-        <v>492.2127661097256</v>
+        <v>494.2869501685552</v>
       </c>
       <c r="E18">
-        <v>-201.276</v>
+        <v>-195.737</v>
       </c>
       <c r="F18">
-        <v>88.624</v>
+        <v>94.163</v>
       </c>
       <c r="G18">
         <v>17.6</v>
@@ -2751,28 +2751,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M18">
-        <v>4.457787199999999</v>
+        <v>4.736398899999999</v>
       </c>
       <c r="N18">
-        <v>82.30887946666668</v>
+        <v>82.03026776666668</v>
       </c>
       <c r="O18">
-        <v>20.52783453898667</v>
+        <v>20.45834878100667</v>
       </c>
       <c r="P18">
-        <v>61.78104492768001</v>
+        <v>61.57191898566001</v>
       </c>
       <c r="Q18">
-        <v>70.18104492768001</v>
+        <v>69.97191898566001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08955589816132904</v>
+        <v>0.08996804541497583</v>
       </c>
       <c r="T18">
-        <v>1.010528825896745</v>
+        <v>1.020047238221151</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.46406653656924</v>
+        <v>18.31912144618282</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08109185829442993</v>
+        <v>0.08091593333334347</v>
       </c>
       <c r="C19">
-        <v>417.7239501685552</v>
+        <v>414.2766894236801</v>
       </c>
       <c r="D19">
-        <v>494.2869501685552</v>
+        <v>496.3786894236801</v>
       </c>
       <c r="E19">
-        <v>-195.737</v>
+        <v>-190.198</v>
       </c>
       <c r="F19">
-        <v>94.163</v>
+        <v>99.70200000000001</v>
       </c>
       <c r="G19">
         <v>17.6</v>
@@ -2833,28 +2833,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M19">
-        <v>4.736398899999999</v>
+        <v>5.0150106</v>
       </c>
       <c r="N19">
-        <v>82.03026776666668</v>
+        <v>81.75165606666668</v>
       </c>
       <c r="O19">
-        <v>20.45834878100667</v>
+        <v>20.38886302302667</v>
       </c>
       <c r="P19">
-        <v>61.57191898566001</v>
+        <v>61.36279304364001</v>
       </c>
       <c r="Q19">
-        <v>69.97191898566001</v>
+        <v>69.76279304364002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08996804541497583</v>
+        <v>0.09039024504066279</v>
       </c>
       <c r="T19">
-        <v>1.020047238221151</v>
+        <v>1.029797806943714</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.31912144618282</v>
+        <v>17.30139247695043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08091593333334349</v>
+        <v>0.08074000837225703</v>
       </c>
       <c r="C20">
-        <v>414.27668942368</v>
+        <v>410.8472076941808</v>
       </c>
       <c r="D20">
-        <v>496.3786894236799</v>
+        <v>498.4882076941808</v>
       </c>
       <c r="E20">
-        <v>-190.198</v>
+        <v>-184.659</v>
       </c>
       <c r="F20">
-        <v>99.702</v>
+        <v>105.241</v>
       </c>
       <c r="G20">
         <v>17.6</v>
@@ -2915,28 +2915,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M20">
-        <v>5.0150106</v>
+        <v>5.2936223</v>
       </c>
       <c r="N20">
-        <v>81.75165606666668</v>
+        <v>81.47304436666668</v>
       </c>
       <c r="O20">
-        <v>20.38886302302667</v>
+        <v>20.31937726504667</v>
       </c>
       <c r="P20">
-        <v>61.36279304364001</v>
+        <v>61.15366710162002</v>
       </c>
       <c r="Q20">
-        <v>69.76279304364002</v>
+        <v>69.55366710162002</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09039024504066279</v>
+        <v>0.09082286934846548</v>
       </c>
       <c r="T20">
-        <v>1.029797806943714</v>
+        <v>1.039789130449549</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.30139247695043</v>
+        <v>16.39079287290041</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08074000837225703</v>
+        <v>0.08056408341117059</v>
       </c>
       <c r="C21">
-        <v>410.8472076941808</v>
+        <v>407.4357326201369</v>
       </c>
       <c r="D21">
-        <v>498.4882076941808</v>
+        <v>500.615732620137</v>
       </c>
       <c r="E21">
-        <v>-184.659</v>
+        <v>-179.12</v>
       </c>
       <c r="F21">
-        <v>105.241</v>
+        <v>110.78</v>
       </c>
       <c r="G21">
         <v>17.6</v>
@@ -2997,28 +2997,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M21">
-        <v>5.2936223</v>
+        <v>5.572234</v>
       </c>
       <c r="N21">
-        <v>81.47304436666668</v>
+        <v>81.19443266666669</v>
       </c>
       <c r="O21">
-        <v>20.31937726504667</v>
+        <v>20.24989150706667</v>
       </c>
       <c r="P21">
-        <v>61.15366710162002</v>
+        <v>60.94454115960001</v>
       </c>
       <c r="Q21">
-        <v>69.55366710162002</v>
+        <v>69.34454115960001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09082286934846548</v>
+        <v>0.09126630926396324</v>
       </c>
       <c r="T21">
-        <v>1.039789130449549</v>
+        <v>1.050030237043031</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.39079287290041</v>
+        <v>15.57125322925539</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08056408341117059</v>
+        <v>0.08038815845008415</v>
       </c>
       <c r="C22">
-        <v>407.4357326201369</v>
+        <v>404.0424957445148</v>
       </c>
       <c r="D22">
-        <v>500.615732620137</v>
+        <v>502.7614957445149</v>
       </c>
       <c r="E22">
-        <v>-179.12</v>
+        <v>-173.581</v>
       </c>
       <c r="F22">
-        <v>110.78</v>
+        <v>116.319</v>
       </c>
       <c r="G22">
         <v>17.6</v>
@@ -3079,28 +3079,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M22">
-        <v>5.572234</v>
+        <v>5.8508457</v>
       </c>
       <c r="N22">
-        <v>81.19443266666669</v>
+        <v>80.91582096666669</v>
       </c>
       <c r="O22">
-        <v>20.24989150706667</v>
+        <v>20.18040574908667</v>
       </c>
       <c r="P22">
-        <v>60.94454115960001</v>
+        <v>60.73541521758001</v>
       </c>
       <c r="Q22">
-        <v>69.34454115960001</v>
+        <v>69.13541521758</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09126630926396324</v>
+        <v>0.09172097550643563</v>
       </c>
       <c r="T22">
-        <v>1.050030237043031</v>
+        <v>1.060530612157867</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.57125322925539</v>
+        <v>14.82976498024323</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08038815845008415</v>
+        <v>0.0802122334889977</v>
       </c>
       <c r="C23">
-        <v>404.0424957445149</v>
+        <v>400.6677325971723</v>
       </c>
       <c r="D23">
-        <v>502.7614957445149</v>
+        <v>504.9257325971724</v>
       </c>
       <c r="E23">
-        <v>-173.581</v>
+        <v>-168.042</v>
       </c>
       <c r="F23">
-        <v>116.319</v>
+        <v>121.858</v>
       </c>
       <c r="G23">
         <v>17.6</v>
@@ -3161,28 +3161,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M23">
-        <v>5.850845699999999</v>
+        <v>6.129457399999999</v>
       </c>
       <c r="N23">
-        <v>80.91582096666669</v>
+        <v>80.63720926666669</v>
       </c>
       <c r="O23">
-        <v>20.18040574908667</v>
+        <v>20.11091999110667</v>
       </c>
       <c r="P23">
-        <v>60.73541521758001</v>
+        <v>60.52628927556002</v>
       </c>
       <c r="Q23">
-        <v>69.13541521758</v>
+        <v>68.92628927556001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09172097550643563</v>
+        <v>0.09218729985768935</v>
       </c>
       <c r="T23">
-        <v>1.060530612157867</v>
+        <v>1.071300227660262</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.82976498024323</v>
+        <v>14.15568475386854</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0802122334889977</v>
+        <v>0.08003630852791123</v>
       </c>
       <c r="C24">
-        <v>400.6677325971723</v>
+        <v>397.3116827810407</v>
       </c>
       <c r="D24">
-        <v>504.9257325971724</v>
+        <v>507.1086827810407</v>
       </c>
       <c r="E24">
-        <v>-168.042</v>
+        <v>-162.503</v>
       </c>
       <c r="F24">
-        <v>121.858</v>
+        <v>127.397</v>
       </c>
       <c r="G24">
         <v>17.6</v>
@@ -3243,28 +3243,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M24">
-        <v>6.129457399999999</v>
+        <v>6.4080691</v>
       </c>
       <c r="N24">
-        <v>80.63720926666669</v>
+        <v>80.35859756666667</v>
       </c>
       <c r="O24">
-        <v>20.11091999110667</v>
+        <v>20.04143423312667</v>
       </c>
       <c r="P24">
-        <v>60.52628927556002</v>
+        <v>60.31716333354001</v>
       </c>
       <c r="Q24">
-        <v>68.92628927556001</v>
+        <v>68.71716333354001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09218729985768935</v>
+        <v>0.09266573652975485</v>
       </c>
       <c r="T24">
-        <v>1.071300227660262</v>
+        <v>1.082349573435447</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.15568475386854</v>
+        <v>13.54022019935251</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08003630852791123</v>
+        <v>0.0798603835668248</v>
       </c>
       <c r="C25">
-        <v>397.3116827810407</v>
+        <v>393.9745900605524</v>
       </c>
       <c r="D25">
-        <v>507.1086827810407</v>
+        <v>509.3105900605524</v>
       </c>
       <c r="E25">
-        <v>-162.503</v>
+        <v>-156.964</v>
       </c>
       <c r="F25">
-        <v>127.397</v>
+        <v>132.936</v>
       </c>
       <c r="G25">
         <v>17.6</v>
@@ -3325,28 +3325,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M25">
-        <v>6.4080691</v>
+        <v>6.6866808</v>
       </c>
       <c r="N25">
-        <v>80.35859756666667</v>
+        <v>80.07998586666668</v>
       </c>
       <c r="O25">
-        <v>20.04143423312667</v>
+        <v>19.97194847514667</v>
       </c>
       <c r="P25">
-        <v>60.31716333354001</v>
+        <v>60.10803739152001</v>
       </c>
       <c r="Q25">
-        <v>68.71716333354001</v>
+        <v>68.50803739152001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09266573652975485</v>
+        <v>0.09315676364055894</v>
       </c>
       <c r="T25">
-        <v>1.082349573435447</v>
+        <v>1.093689691467874</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.54022019935251</v>
+        <v>12.97604435771282</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0798603835668248</v>
+        <v>0.07996593360573834</v>
       </c>
       <c r="C26">
-        <v>393.9745900605524</v>
+        <v>387.1122187964617</v>
       </c>
       <c r="D26">
-        <v>509.3105900605524</v>
+        <v>507.9872187964617</v>
       </c>
       <c r="E26">
-        <v>-156.964</v>
+        <v>-151.425</v>
       </c>
       <c r="F26">
-        <v>132.936</v>
+        <v>138.475</v>
       </c>
       <c r="G26">
         <v>17.6</v>
@@ -3407,45 +3407,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M26">
-        <v>6.686680799999999</v>
+        <v>7.173005</v>
       </c>
       <c r="N26">
-        <v>80.07998586666668</v>
+        <v>79.59366166666668</v>
       </c>
       <c r="O26">
-        <v>19.97194847514667</v>
+        <v>19.85065921966667</v>
       </c>
       <c r="P26">
-        <v>60.10803739152001</v>
+        <v>59.74300244700001</v>
       </c>
       <c r="Q26">
-        <v>68.50803739152001</v>
+        <v>68.14300244700001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09315676364055894</v>
+        <v>0.09366088480765111</v>
       </c>
       <c r="T26">
-        <v>1.093689691467874</v>
+        <v>1.105332212647832</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.97604435771283</v>
+        <v>12.09627857037137</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07996593360573834</v>
+        <v>0.07980126764465188</v>
       </c>
       <c r="C27">
-        <v>387.1122187964617</v>
+        <v>383.6407937509463</v>
       </c>
       <c r="D27">
-        <v>507.9872187964617</v>
+        <v>510.0547937509463</v>
       </c>
       <c r="E27">
-        <v>-151.425</v>
+        <v>-145.886</v>
       </c>
       <c r="F27">
-        <v>138.475</v>
+        <v>144.014</v>
       </c>
       <c r="G27">
         <v>17.6</v>
@@ -3489,28 +3489,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M27">
-        <v>7.173005</v>
+        <v>7.459925200000001</v>
       </c>
       <c r="N27">
-        <v>79.59366166666668</v>
+        <v>79.30674146666668</v>
       </c>
       <c r="O27">
-        <v>19.85065921966667</v>
+        <v>19.77910132178667</v>
       </c>
       <c r="P27">
-        <v>59.74300244700001</v>
+        <v>59.52764014488001</v>
       </c>
       <c r="Q27">
-        <v>68.14300244700001</v>
+        <v>67.92764014488</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09366088480765111</v>
+        <v>0.09417863087115119</v>
       </c>
       <c r="T27">
-        <v>1.105332212647832</v>
+        <v>1.117289396562383</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.09627857037137</v>
+        <v>11.63103708689555</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07980126764465188</v>
+        <v>0.07963660168356543</v>
       </c>
       <c r="C28">
-        <v>383.6407937509463</v>
+        <v>380.1862680934836</v>
       </c>
       <c r="D28">
-        <v>510.0547937509463</v>
+        <v>512.1392680934836</v>
       </c>
       <c r="E28">
-        <v>-145.886</v>
+        <v>-140.347</v>
       </c>
       <c r="F28">
-        <v>144.014</v>
+        <v>149.553</v>
       </c>
       <c r="G28">
         <v>17.6</v>
@@ -3571,28 +3571,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M28">
-        <v>7.459925200000001</v>
+        <v>7.7468454</v>
       </c>
       <c r="N28">
-        <v>79.30674146666668</v>
+        <v>79.01982126666668</v>
       </c>
       <c r="O28">
-        <v>19.77910132178667</v>
+        <v>19.70754342390667</v>
       </c>
       <c r="P28">
-        <v>59.52764014488001</v>
+        <v>59.31227784276001</v>
       </c>
       <c r="Q28">
-        <v>67.92764014488</v>
+        <v>67.71227784276002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09417863087115119</v>
+        <v>0.0947105617583088</v>
       </c>
       <c r="T28">
-        <v>1.117289396562383</v>
+        <v>1.129574174556786</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.63103708689555</v>
+        <v>11.20025793552905</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07963660168356543</v>
+        <v>0.07947193572247899</v>
       </c>
       <c r="C29">
-        <v>380.1862680934836</v>
+        <v>376.7488498658004</v>
       </c>
       <c r="D29">
-        <v>512.1392680934836</v>
+        <v>514.2408498658003</v>
       </c>
       <c r="E29">
-        <v>-140.347</v>
+        <v>-134.808</v>
       </c>
       <c r="F29">
-        <v>149.553</v>
+        <v>155.092</v>
       </c>
       <c r="G29">
         <v>17.6</v>
@@ -3653,28 +3653,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M29">
-        <v>7.7468454</v>
+        <v>8.033765600000001</v>
       </c>
       <c r="N29">
-        <v>79.01982126666668</v>
+        <v>78.73290106666668</v>
       </c>
       <c r="O29">
-        <v>19.70754342390667</v>
+        <v>19.63598552602667</v>
       </c>
       <c r="P29">
-        <v>59.31227784276001</v>
+        <v>59.09691554064001</v>
       </c>
       <c r="Q29">
-        <v>67.71227784276002</v>
+        <v>67.49691554064</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0947105617583088</v>
+        <v>0.09525726850344303</v>
       </c>
       <c r="T29">
-        <v>1.129574174556786</v>
+        <v>1.142200196384366</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.20025793552905</v>
+        <v>10.80024872354586</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07947193572247899</v>
+        <v>0.07930726976139252</v>
       </c>
       <c r="C30">
-        <v>376.7488498658004</v>
+        <v>373.328750538521</v>
       </c>
       <c r="D30">
-        <v>514.2408498658003</v>
+        <v>516.359750538521</v>
       </c>
       <c r="E30">
-        <v>-134.808</v>
+        <v>-129.269</v>
       </c>
       <c r="F30">
-        <v>155.092</v>
+        <v>160.631</v>
       </c>
       <c r="G30">
         <v>17.6</v>
@@ -3735,28 +3735,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M30">
-        <v>8.033765600000001</v>
+        <v>8.3206858</v>
       </c>
       <c r="N30">
-        <v>78.73290106666668</v>
+        <v>78.44598086666667</v>
       </c>
       <c r="O30">
-        <v>19.63598552602667</v>
+        <v>19.56442762814667</v>
       </c>
       <c r="P30">
-        <v>59.09691554064001</v>
+        <v>58.88155323852001</v>
       </c>
       <c r="Q30">
-        <v>67.49691554064</v>
+        <v>67.28155323852</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09525726850344303</v>
+        <v>0.09581937543858102</v>
       </c>
       <c r="T30">
-        <v>1.142200196384366</v>
+        <v>1.155181880798638</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.80024872354586</v>
+        <v>10.42782635376842</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07930726976139252</v>
+        <v>0.07914260380030608</v>
       </c>
       <c r="C31">
-        <v>373.328750538521</v>
+        <v>369.9261850821014</v>
       </c>
       <c r="D31">
-        <v>516.359750538521</v>
+        <v>518.4961850821013</v>
       </c>
       <c r="E31">
-        <v>-129.269</v>
+        <v>-123.73</v>
       </c>
       <c r="F31">
-        <v>160.631</v>
+        <v>166.17</v>
       </c>
       <c r="G31">
         <v>17.6</v>
@@ -3817,28 +3817,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M31">
-        <v>8.320685799999998</v>
+        <v>8.607605999999999</v>
       </c>
       <c r="N31">
-        <v>78.44598086666669</v>
+        <v>78.15906066666668</v>
       </c>
       <c r="O31">
-        <v>19.56442762814667</v>
+        <v>19.49286973026667</v>
       </c>
       <c r="P31">
-        <v>58.88155323852001</v>
+        <v>58.66619093640001</v>
       </c>
       <c r="Q31">
-        <v>67.28155323852002</v>
+        <v>67.06619093640001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09581937543858102</v>
+        <v>0.09639754257186582</v>
       </c>
       <c r="T31">
-        <v>1.155181880798638</v>
+        <v>1.16853447048189</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.42782635376842</v>
+        <v>10.08023214197614</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07914260380030608</v>
+        <v>0.07937350403921961</v>
       </c>
       <c r="C32">
-        <v>369.9261850821014</v>
+        <v>361.3963604850107</v>
       </c>
       <c r="D32">
-        <v>518.4961850821013</v>
+        <v>515.5053604850107</v>
       </c>
       <c r="E32">
-        <v>-123.73</v>
+        <v>-118.191</v>
       </c>
       <c r="F32">
-        <v>166.17</v>
+        <v>171.709</v>
       </c>
       <c r="G32">
         <v>17.6</v>
@@ -3899,45 +3899,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M32">
-        <v>8.607605999999999</v>
+        <v>9.186431499999999</v>
       </c>
       <c r="N32">
-        <v>78.15906066666668</v>
+        <v>77.58023516666668</v>
       </c>
       <c r="O32">
-        <v>19.49286973026667</v>
+        <v>19.34851065056667</v>
       </c>
       <c r="P32">
-        <v>58.66619093640001</v>
+        <v>58.23172451610002</v>
       </c>
       <c r="Q32">
-        <v>67.06619093640001</v>
+        <v>66.63172451610001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09639754257186582</v>
+        <v>0.09699246817278206</v>
       </c>
       <c r="T32">
-        <v>1.16853447048189</v>
+        <v>1.182274091750163</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.08023214197614</v>
+        <v>9.445089387175715</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07937350403921961</v>
+        <v>0.07922159827813316</v>
       </c>
       <c r="C33">
-        <v>361.3963604850107</v>
+        <v>357.82108086131</v>
       </c>
       <c r="D33">
-        <v>515.5053604850107</v>
+        <v>517.46908086131</v>
       </c>
       <c r="E33">
-        <v>-118.191</v>
+        <v>-112.652</v>
       </c>
       <c r="F33">
-        <v>171.709</v>
+        <v>177.248</v>
       </c>
       <c r="G33">
         <v>17.6</v>
@@ -3981,28 +3981,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M33">
-        <v>9.186431499999999</v>
+        <v>9.482768</v>
       </c>
       <c r="N33">
-        <v>77.58023516666668</v>
+        <v>77.28389866666669</v>
       </c>
       <c r="O33">
-        <v>19.34851065056667</v>
+        <v>19.27460432746667</v>
       </c>
       <c r="P33">
-        <v>58.23172451610002</v>
+        <v>58.00929433920001</v>
       </c>
       <c r="Q33">
-        <v>66.63172451610001</v>
+        <v>66.40929433920002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09699246817278206</v>
+        <v>0.09760489158548996</v>
       </c>
       <c r="T33">
-        <v>1.182274091750163</v>
+        <v>1.196417819526327</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.445089387175715</v>
+        <v>9.149930343826474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07922159827813316</v>
+        <v>0.07906969251704672</v>
       </c>
       <c r="C34">
-        <v>357.82108086131</v>
+        <v>354.2608192903439</v>
       </c>
       <c r="D34">
-        <v>517.46908086131</v>
+        <v>519.4478192903439</v>
       </c>
       <c r="E34">
-        <v>-112.652</v>
+        <v>-107.113</v>
       </c>
       <c r="F34">
-        <v>177.248</v>
+        <v>182.787</v>
       </c>
       <c r="G34">
         <v>17.6</v>
@@ -4063,28 +4063,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M34">
-        <v>9.482768</v>
+        <v>9.779104500000001</v>
       </c>
       <c r="N34">
-        <v>77.28389866666669</v>
+        <v>76.98756216666668</v>
       </c>
       <c r="O34">
-        <v>19.27460432746667</v>
+        <v>19.20069800436667</v>
       </c>
       <c r="P34">
-        <v>58.00929433920001</v>
+        <v>57.78686416230001</v>
       </c>
       <c r="Q34">
-        <v>66.40929433920002</v>
+        <v>66.1868641623</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09760489158548996</v>
+        <v>0.09823559629409959</v>
       </c>
       <c r="T34">
-        <v>1.196417819526327</v>
+        <v>1.21098374813163</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.149930343826474</v>
+        <v>8.872659727346882</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07906969251704672</v>
+        <v>0.07891778675596026</v>
       </c>
       <c r="C35">
-        <v>354.2608192903439</v>
+        <v>350.7157487150117</v>
       </c>
       <c r="D35">
-        <v>519.4478192903439</v>
+        <v>521.4417487150117</v>
       </c>
       <c r="E35">
-        <v>-107.113</v>
+        <v>-101.574</v>
       </c>
       <c r="F35">
-        <v>182.787</v>
+        <v>188.326</v>
       </c>
       <c r="G35">
         <v>17.6</v>
@@ -4145,28 +4145,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M35">
-        <v>9.779104500000001</v>
+        <v>10.075441</v>
       </c>
       <c r="N35">
-        <v>76.98756216666668</v>
+        <v>76.69122566666668</v>
       </c>
       <c r="O35">
-        <v>19.20069800436667</v>
+        <v>19.12679168126667</v>
       </c>
       <c r="P35">
-        <v>57.78686416230001</v>
+        <v>57.56443398540002</v>
       </c>
       <c r="Q35">
-        <v>66.1868641623</v>
+        <v>65.96443398540001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09823559629409959</v>
+        <v>0.09888541326660646</v>
       </c>
       <c r="T35">
-        <v>1.21098374813163</v>
+        <v>1.225991068512852</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.872659727346882</v>
+        <v>8.6116991471308</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07891778675596026</v>
+        <v>0.0787658809948738</v>
       </c>
       <c r="C36">
-        <v>350.7157487150117</v>
+        <v>347.186044743848</v>
       </c>
       <c r="D36">
-        <v>521.4417487150117</v>
+        <v>523.451044743848</v>
       </c>
       <c r="E36">
-        <v>-101.574</v>
+        <v>-96.03499999999997</v>
       </c>
       <c r="F36">
-        <v>188.326</v>
+        <v>193.865</v>
       </c>
       <c r="G36">
         <v>17.6</v>
@@ -4227,28 +4227,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M36">
-        <v>10.075441</v>
+        <v>10.3717775</v>
       </c>
       <c r="N36">
-        <v>76.69122566666668</v>
+        <v>76.39488916666667</v>
       </c>
       <c r="O36">
-        <v>19.12679168126667</v>
+        <v>19.05288535816667</v>
       </c>
       <c r="P36">
-        <v>57.56443398540002</v>
+        <v>57.3420038085</v>
       </c>
       <c r="Q36">
-        <v>65.96443398540001</v>
+        <v>65.7420038085</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09888541326660646</v>
+        <v>0.09955522460749819</v>
       </c>
       <c r="T36">
-        <v>1.225991068512852</v>
+        <v>1.241460152598111</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.6116991471308</v>
+        <v>8.365650600069918</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0787658809948738</v>
+        <v>0.07861397523378735</v>
       </c>
       <c r="C37">
-        <v>347.186044743848</v>
+        <v>343.671885702581</v>
       </c>
       <c r="D37">
-        <v>523.451044743848</v>
+        <v>525.475885702581</v>
       </c>
       <c r="E37">
-        <v>-96.03499999999997</v>
+        <v>-90.49599999999995</v>
       </c>
       <c r="F37">
-        <v>193.865</v>
+        <v>199.404</v>
       </c>
       <c r="G37">
         <v>17.6</v>
@@ -4309,28 +4309,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M37">
-        <v>10.3717775</v>
+        <v>10.668114</v>
       </c>
       <c r="N37">
-        <v>76.39488916666667</v>
+        <v>76.09855266666668</v>
       </c>
       <c r="O37">
-        <v>19.05288535816667</v>
+        <v>18.97897903506667</v>
       </c>
       <c r="P37">
-        <v>57.3420038085</v>
+        <v>57.11957363160001</v>
       </c>
       <c r="Q37">
-        <v>65.7420038085</v>
+        <v>65.5195736316</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09955522460749819</v>
+        <v>0.1002459675527928</v>
       </c>
       <c r="T37">
-        <v>1.241460152598111</v>
+        <v>1.257412645561034</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.365650600069918</v>
+        <v>8.133271416734642</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07861397523378737</v>
+        <v>0.07846206947270092</v>
       </c>
       <c r="C38">
-        <v>343.6718857025808</v>
+        <v>340.1734526868889</v>
       </c>
       <c r="D38">
-        <v>525.4758857025807</v>
+        <v>527.5164526868889</v>
       </c>
       <c r="E38">
-        <v>-90.49599999999998</v>
+        <v>-84.95699999999999</v>
       </c>
       <c r="F38">
-        <v>199.404</v>
+        <v>204.943</v>
       </c>
       <c r="G38">
         <v>17.6</v>
@@ -4391,28 +4391,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M38">
-        <v>10.668114</v>
+        <v>10.9644505</v>
       </c>
       <c r="N38">
-        <v>76.09855266666668</v>
+        <v>75.80221616666668</v>
       </c>
       <c r="O38">
-        <v>18.97897903506667</v>
+        <v>18.90507271196667</v>
       </c>
       <c r="P38">
-        <v>57.11957363160001</v>
+        <v>56.89714345470001</v>
       </c>
       <c r="Q38">
-        <v>65.5195736316</v>
+        <v>65.29714345470001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1002459675527928</v>
+        <v>0.100958638845557</v>
       </c>
       <c r="T38">
-        <v>1.257412645561034</v>
+        <v>1.273871566871986</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.133271416734644</v>
+        <v>7.913453270336411</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07846206947270092</v>
+        <v>0.07831016371161446</v>
       </c>
       <c r="C39">
-        <v>340.1734526868889</v>
+        <v>336.690929616394</v>
       </c>
       <c r="D39">
-        <v>527.5164526868889</v>
+        <v>529.5729296163939</v>
       </c>
       <c r="E39">
-        <v>-84.95699999999999</v>
+        <v>-79.41799999999998</v>
       </c>
       <c r="F39">
-        <v>204.943</v>
+        <v>210.482</v>
       </c>
       <c r="G39">
         <v>17.6</v>
@@ -4473,28 +4473,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M39">
-        <v>10.9644505</v>
+        <v>11.260787</v>
       </c>
       <c r="N39">
-        <v>75.80221616666668</v>
+        <v>75.50587966666669</v>
       </c>
       <c r="O39">
-        <v>18.90507271196667</v>
+        <v>18.83116638886667</v>
       </c>
       <c r="P39">
-        <v>56.89714345470001</v>
+        <v>56.67471327780001</v>
       </c>
       <c r="Q39">
-        <v>65.29714345470001</v>
+        <v>65.07471327780002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.100958638845557</v>
+        <v>0.101694299534862</v>
       </c>
       <c r="T39">
-        <v>1.273871566871986</v>
+        <v>1.290861421128454</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.913453270336411</v>
+        <v>7.705204500064399</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07831016371161446</v>
+        <v>0.078392445150528</v>
       </c>
       <c r="C40">
-        <v>336.690929616394</v>
+        <v>330.0360299572339</v>
       </c>
       <c r="D40">
-        <v>529.5729296163939</v>
+        <v>528.4570299572339</v>
       </c>
       <c r="E40">
-        <v>-79.41799999999998</v>
+        <v>-73.87899999999999</v>
       </c>
       <c r="F40">
-        <v>210.482</v>
+        <v>216.021</v>
       </c>
       <c r="G40">
         <v>17.6</v>
@@ -4555,45 +4555,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M40">
-        <v>11.260787</v>
+        <v>11.7299403</v>
       </c>
       <c r="N40">
-        <v>75.50587966666669</v>
+        <v>75.03672636666668</v>
       </c>
       <c r="O40">
-        <v>18.83116638886667</v>
+        <v>18.71415955584667</v>
       </c>
       <c r="P40">
-        <v>56.67471327780001</v>
+        <v>56.32256681082001</v>
       </c>
       <c r="Q40">
-        <v>65.07471327780002</v>
+        <v>64.72256681082001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.101694299534862</v>
+        <v>0.1024540802467672</v>
       </c>
       <c r="T40">
-        <v>1.290861421128454</v>
+        <v>1.308408319786772</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.705204500064399</v>
+        <v>7.397025427884461</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.078392445150528</v>
+        <v>0.07824654418944156</v>
       </c>
       <c r="C41">
-        <v>330.0360299572339</v>
+        <v>326.4789725361224</v>
       </c>
       <c r="D41">
-        <v>528.4570299572339</v>
+        <v>530.4389725361224</v>
       </c>
       <c r="E41">
-        <v>-73.87899999999999</v>
+        <v>-68.33999999999997</v>
       </c>
       <c r="F41">
-        <v>216.021</v>
+        <v>221.56</v>
       </c>
       <c r="G41">
         <v>17.6</v>
@@ -4637,28 +4637,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M41">
-        <v>11.7299403</v>
+        <v>12.030708</v>
       </c>
       <c r="N41">
-        <v>75.03672636666668</v>
+        <v>74.73595866666668</v>
       </c>
       <c r="O41">
-        <v>18.71415955584667</v>
+        <v>18.63914809146667</v>
       </c>
       <c r="P41">
-        <v>56.32256681082001</v>
+        <v>56.09681057520001</v>
       </c>
       <c r="Q41">
-        <v>64.72256681082001</v>
+        <v>64.49681057520002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1024540802467672</v>
+        <v>0.1032391869824026</v>
       </c>
       <c r="T41">
-        <v>1.308408319786772</v>
+        <v>1.326540115067035</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.397025427884461</v>
+        <v>7.212099792187349</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07824654418944156</v>
+        <v>0.07810064322835511</v>
       </c>
       <c r="C42">
-        <v>326.4789725361224</v>
+        <v>322.9368373648201</v>
       </c>
       <c r="D42">
-        <v>530.4389725361224</v>
+        <v>532.4358373648201</v>
       </c>
       <c r="E42">
-        <v>-68.33999999999997</v>
+        <v>-62.80099999999996</v>
       </c>
       <c r="F42">
-        <v>221.56</v>
+        <v>227.099</v>
       </c>
       <c r="G42">
         <v>17.6</v>
@@ -4719,28 +4719,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M42">
-        <v>12.030708</v>
+        <v>12.3314757</v>
       </c>
       <c r="N42">
-        <v>74.73595866666668</v>
+        <v>74.43519096666668</v>
       </c>
       <c r="O42">
-        <v>18.63914809146667</v>
+        <v>18.56413662708667</v>
       </c>
       <c r="P42">
-        <v>56.09681057520001</v>
+        <v>55.87105433958001</v>
       </c>
       <c r="Q42">
-        <v>64.49681057520002</v>
+        <v>64.27105433958002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1032391869824026</v>
+        <v>0.1040509075056866</v>
       </c>
       <c r="T42">
-        <v>1.326540115067035</v>
+        <v>1.345286547475442</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.212099792187349</v>
+        <v>7.03619491920717</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07810064322835511</v>
+        <v>0.07795474226726865</v>
       </c>
       <c r="C43">
-        <v>322.9368373648201</v>
+        <v>319.4097936068855</v>
       </c>
       <c r="D43">
-        <v>532.4358373648201</v>
+        <v>534.4477936068855</v>
       </c>
       <c r="E43">
-        <v>-62.80099999999996</v>
+        <v>-57.26199999999997</v>
       </c>
       <c r="F43">
-        <v>227.099</v>
+        <v>232.638</v>
       </c>
       <c r="G43">
         <v>17.6</v>
@@ -4801,28 +4801,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M43">
-        <v>12.3314757</v>
+        <v>12.6322434</v>
       </c>
       <c r="N43">
-        <v>74.43519096666668</v>
+        <v>74.13442326666669</v>
       </c>
       <c r="O43">
-        <v>18.56413662708667</v>
+        <v>18.48912516270667</v>
       </c>
       <c r="P43">
-        <v>55.87105433958001</v>
+        <v>55.64529810396002</v>
       </c>
       <c r="Q43">
-        <v>64.27105433958002</v>
+        <v>64.04529810396002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1040509075056866</v>
+        <v>0.1048906183918425</v>
       </c>
       <c r="T43">
-        <v>1.345286547475442</v>
+        <v>1.364679408587587</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.03619491920717</v>
+        <v>6.868666468749857</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07795474226726865</v>
+        <v>0.07780884130618219</v>
       </c>
       <c r="C44">
-        <v>319.4097936068856</v>
+        <v>315.8980129925006</v>
       </c>
       <c r="D44">
-        <v>534.4477936068855</v>
+        <v>536.4750129925006</v>
       </c>
       <c r="E44">
-        <v>-57.262</v>
+        <v>-51.72299999999998</v>
       </c>
       <c r="F44">
-        <v>232.638</v>
+        <v>238.177</v>
       </c>
       <c r="G44">
         <v>17.6</v>
@@ -4883,28 +4883,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M44">
-        <v>12.6322434</v>
+        <v>12.9330111</v>
       </c>
       <c r="N44">
-        <v>74.13442326666669</v>
+        <v>73.83365556666668</v>
       </c>
       <c r="O44">
-        <v>18.48912516270667</v>
+        <v>18.41411369832667</v>
       </c>
       <c r="P44">
-        <v>55.64529810396002</v>
+        <v>55.41954186834</v>
       </c>
       <c r="Q44">
-        <v>64.04529810396002</v>
+        <v>63.81954186834</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1048906183918425</v>
+        <v>0.1057597928178635</v>
       </c>
       <c r="T44">
-        <v>1.364679408587587</v>
+        <v>1.384752720966825</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.868666468749858</v>
+        <v>6.708930039244046</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07780884130618219</v>
+        <v>0.07766294034509574</v>
       </c>
       <c r="C45">
-        <v>315.8980129925006</v>
+        <v>312.4016698673355</v>
       </c>
       <c r="D45">
-        <v>536.4750129925006</v>
+        <v>538.5176698673355</v>
       </c>
       <c r="E45">
-        <v>-51.72299999999998</v>
+        <v>-46.184</v>
       </c>
       <c r="F45">
-        <v>238.177</v>
+        <v>243.716</v>
       </c>
       <c r="G45">
         <v>17.6</v>
@@ -4965,28 +4965,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M45">
-        <v>12.9330111</v>
+        <v>13.2337788</v>
       </c>
       <c r="N45">
-        <v>73.83365556666668</v>
+        <v>73.53288786666668</v>
       </c>
       <c r="O45">
-        <v>18.41411369832667</v>
+        <v>18.33910223394667</v>
       </c>
       <c r="P45">
-        <v>55.41954186834</v>
+        <v>55.19378563272001</v>
       </c>
       <c r="Q45">
-        <v>63.81954186834</v>
+        <v>63.59378563272001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1057597928178635</v>
+        <v>0.106660009187671</v>
       </c>
       <c r="T45">
-        <v>1.384752720966825</v>
+        <v>1.405542937359607</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.708930039244046</v>
+        <v>6.556454356533954</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07766294034509574</v>
+        <v>0.07751703938400931</v>
       </c>
       <c r="C46">
-        <v>312.4016698673355</v>
+        <v>308.9209412425295</v>
       </c>
       <c r="D46">
-        <v>538.5176698673355</v>
+        <v>540.5759412425294</v>
       </c>
       <c r="E46">
-        <v>-46.184</v>
+        <v>-40.64499999999998</v>
       </c>
       <c r="F46">
-        <v>243.716</v>
+        <v>249.255</v>
       </c>
       <c r="G46">
         <v>17.6</v>
@@ -5047,28 +5047,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M46">
-        <v>13.2337788</v>
+        <v>13.5345465</v>
       </c>
       <c r="N46">
-        <v>73.53288786666668</v>
+        <v>73.23212016666668</v>
       </c>
       <c r="O46">
-        <v>18.33910223394667</v>
+        <v>18.26409076956667</v>
       </c>
       <c r="P46">
-        <v>55.19378563272001</v>
+        <v>54.9680293971</v>
       </c>
       <c r="Q46">
-        <v>63.59378563272001</v>
+        <v>63.3680293971</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.106660009187671</v>
+        <v>0.1075929606981987</v>
       </c>
       <c r="T46">
-        <v>1.405542937359607</v>
+        <v>1.427089161621218</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.556454356533954</v>
+        <v>6.410755370833199</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07751703938400931</v>
+        <v>0.07737113842292286</v>
       </c>
       <c r="C47">
-        <v>308.9209412425295</v>
+        <v>305.4560068458269</v>
       </c>
       <c r="D47">
-        <v>540.5759412425294</v>
+        <v>542.6500068458269</v>
       </c>
       <c r="E47">
-        <v>-40.64499999999998</v>
+        <v>-35.10599999999997</v>
       </c>
       <c r="F47">
-        <v>249.255</v>
+        <v>254.794</v>
       </c>
       <c r="G47">
         <v>17.6</v>
@@ -5129,28 +5129,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M47">
-        <v>13.5345465</v>
+        <v>13.8353142</v>
       </c>
       <c r="N47">
-        <v>73.23212016666668</v>
+        <v>72.93135246666668</v>
       </c>
       <c r="O47">
-        <v>18.26409076956667</v>
+        <v>18.18907930518667</v>
       </c>
       <c r="P47">
-        <v>54.9680293971</v>
+        <v>54.74227316148001</v>
       </c>
       <c r="Q47">
-        <v>63.3680293971</v>
+        <v>63.14227316148001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1075929606981987</v>
+        <v>0.1085604659683757</v>
       </c>
       <c r="T47">
-        <v>1.427089161621218</v>
+        <v>1.449433394188814</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.410755370833199</v>
+        <v>6.271391123641173</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07737113842292286</v>
+        <v>0.07722523746183639</v>
       </c>
       <c r="C48">
-        <v>305.4560068458269</v>
+        <v>302.0070491738912</v>
       </c>
       <c r="D48">
-        <v>542.6500068458269</v>
+        <v>544.7400491738912</v>
       </c>
       <c r="E48">
-        <v>-35.10599999999997</v>
+        <v>-29.56699999999995</v>
       </c>
       <c r="F48">
-        <v>254.794</v>
+        <v>260.333</v>
       </c>
       <c r="G48">
         <v>17.6</v>
@@ -5211,28 +5211,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M48">
-        <v>13.8353142</v>
+        <v>14.1360819</v>
       </c>
       <c r="N48">
-        <v>72.93135246666668</v>
+        <v>72.63058476666667</v>
       </c>
       <c r="O48">
-        <v>18.18907930518667</v>
+        <v>18.11406784080667</v>
       </c>
       <c r="P48">
-        <v>54.74227316148001</v>
+        <v>54.51651692586</v>
       </c>
       <c r="Q48">
-        <v>63.14227316148001</v>
+        <v>62.91651692586</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1085604659683757</v>
+        <v>0.1095644808713894</v>
       </c>
       <c r="T48">
-        <v>1.449433394188814</v>
+        <v>1.472620805343867</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.271391123641173</v>
+        <v>6.137957269946678</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07722523746183639</v>
+        <v>0.07743962450074995</v>
       </c>
       <c r="C49">
-        <v>302.0070491738912</v>
+        <v>293.4024596676034</v>
       </c>
       <c r="D49">
-        <v>544.7400491738912</v>
+        <v>541.6744596676034</v>
       </c>
       <c r="E49">
-        <v>-29.56699999999995</v>
+        <v>-24.02799999999996</v>
       </c>
       <c r="F49">
-        <v>260.333</v>
+        <v>265.872</v>
       </c>
       <c r="G49">
         <v>17.6</v>
@@ -5293,45 +5293,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M49">
-        <v>14.1360819</v>
+        <v>14.7027216</v>
       </c>
       <c r="N49">
-        <v>72.63058476666667</v>
+        <v>72.06394506666668</v>
       </c>
       <c r="O49">
-        <v>18.11406784080667</v>
+        <v>17.97274789962667</v>
       </c>
       <c r="P49">
-        <v>54.51651692586</v>
+        <v>54.09119716704001</v>
       </c>
       <c r="Q49">
-        <v>62.91651692586</v>
+        <v>62.49119716704001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1095644808713894</v>
+        <v>0.1106071117322114</v>
       </c>
       <c r="T49">
-        <v>1.472620805343867</v>
+        <v>1.496700040004883</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.137957269946678</v>
+        <v>5.901401728688563</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07743962450074995</v>
+        <v>0.07730122953966349</v>
       </c>
       <c r="C50">
-        <v>293.4024596676035</v>
+        <v>289.8384519443508</v>
       </c>
       <c r="D50">
-        <v>541.6744596676034</v>
+        <v>543.6494519443507</v>
       </c>
       <c r="E50">
-        <v>-24.02800000000002</v>
+        <v>-18.48899999999998</v>
       </c>
       <c r="F50">
-        <v>265.872</v>
+        <v>271.411</v>
       </c>
       <c r="G50">
         <v>17.6</v>
@@ -5375,28 +5375,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M50">
-        <v>14.7027216</v>
+        <v>15.0090283</v>
       </c>
       <c r="N50">
-        <v>72.06394506666668</v>
+        <v>71.75763836666668</v>
       </c>
       <c r="O50">
-        <v>17.97274789962667</v>
+        <v>17.89635500864667</v>
       </c>
       <c r="P50">
-        <v>54.09119716704001</v>
+        <v>53.86128335802001</v>
       </c>
       <c r="Q50">
-        <v>62.49119716704001</v>
+        <v>62.26128335802001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1106071117322114</v>
+        <v>0.1116906300777716</v>
       </c>
       <c r="T50">
-        <v>1.496700040004883</v>
+        <v>1.521723558378096</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.901401728688564</v>
+        <v>5.780964958715328</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07730122953966349</v>
+        <v>0.07716283457857705</v>
       </c>
       <c r="C51">
-        <v>289.8384519443508</v>
+        <v>286.2888989120096</v>
       </c>
       <c r="D51">
-        <v>543.6494519443507</v>
+        <v>545.6388989120096</v>
       </c>
       <c r="E51">
-        <v>-18.48899999999998</v>
+        <v>-12.94999999999999</v>
       </c>
       <c r="F51">
-        <v>271.411</v>
+        <v>276.95</v>
       </c>
       <c r="G51">
         <v>17.6</v>
@@ -5457,28 +5457,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M51">
-        <v>15.0090283</v>
+        <v>15.315335</v>
       </c>
       <c r="N51">
-        <v>71.75763836666668</v>
+        <v>71.45133166666668</v>
       </c>
       <c r="O51">
-        <v>17.89635500864667</v>
+        <v>17.81996211766667</v>
       </c>
       <c r="P51">
-        <v>53.86128335802001</v>
+        <v>53.63136954900001</v>
       </c>
       <c r="Q51">
-        <v>62.26128335802001</v>
+        <v>62.031369549</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1116906300777716</v>
+        <v>0.1128174891571541</v>
       </c>
       <c r="T51">
-        <v>1.521723558378096</v>
+        <v>1.547748017486238</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.780964958715328</v>
+        <v>5.66534565954102</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07716283457857705</v>
+        <v>0.0770244396174906</v>
       </c>
       <c r="C52">
-        <v>286.2888989120096</v>
+        <v>282.7539598411971</v>
       </c>
       <c r="D52">
-        <v>545.6388989120096</v>
+        <v>547.642959841197</v>
       </c>
       <c r="E52">
-        <v>-12.94999999999999</v>
+        <v>-7.411000000000001</v>
       </c>
       <c r="F52">
-        <v>276.95</v>
+        <v>282.489</v>
       </c>
       <c r="G52">
         <v>17.6</v>
@@ -5539,28 +5539,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M52">
-        <v>15.315335</v>
+        <v>15.6216417</v>
       </c>
       <c r="N52">
-        <v>71.45133166666668</v>
+        <v>71.14502496666668</v>
       </c>
       <c r="O52">
-        <v>17.81996211766667</v>
+        <v>17.74356922668667</v>
       </c>
       <c r="P52">
-        <v>53.63136954900001</v>
+        <v>53.40145573998001</v>
       </c>
       <c r="Q52">
-        <v>62.031369549</v>
+        <v>61.80145573998001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1128174891571541</v>
+        <v>0.1139903424846747</v>
       </c>
       <c r="T52">
-        <v>1.547748017486238</v>
+        <v>1.57483469941512</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.66534565954102</v>
+        <v>5.554260450530413</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0770244396174906</v>
+        <v>0.07688604465640413</v>
       </c>
       <c r="C53">
-        <v>282.7539598411971</v>
+        <v>279.2337963510772</v>
       </c>
       <c r="D53">
-        <v>547.642959841197</v>
+        <v>549.6617963510772</v>
       </c>
       <c r="E53">
-        <v>-7.411000000000001</v>
+        <v>-1.871999999999957</v>
       </c>
       <c r="F53">
-        <v>282.489</v>
+        <v>288.028</v>
       </c>
       <c r="G53">
         <v>17.6</v>
@@ -5621,28 +5621,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M53">
-        <v>15.6216417</v>
+        <v>15.9279484</v>
       </c>
       <c r="N53">
-        <v>71.14502496666668</v>
+        <v>70.83871826666667</v>
       </c>
       <c r="O53">
-        <v>17.74356922668667</v>
+        <v>17.66717633570667</v>
       </c>
       <c r="P53">
-        <v>53.40145573998001</v>
+        <v>53.17154193096</v>
       </c>
       <c r="Q53">
-        <v>61.80145573998001</v>
+        <v>61.57154193096</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1139903424846747</v>
+        <v>0.1152120647008419</v>
       </c>
       <c r="T53">
-        <v>1.57483469941512</v>
+        <v>1.603049993091038</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.554260450530413</v>
+        <v>5.447447749558673</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07688604465640413</v>
+        <v>0.07674764969531768</v>
       </c>
       <c r="C54">
-        <v>279.2337963510772</v>
+        <v>275.7285724528091</v>
       </c>
       <c r="D54">
-        <v>549.6617963510772</v>
+        <v>551.6955724528091</v>
       </c>
       <c r="E54">
-        <v>-1.871999999999957</v>
+        <v>3.66700000000003</v>
       </c>
       <c r="F54">
-        <v>288.028</v>
+        <v>293.567</v>
       </c>
       <c r="G54">
         <v>17.6</v>
@@ -5703,28 +5703,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M54">
-        <v>15.9279484</v>
+        <v>16.2342551</v>
       </c>
       <c r="N54">
-        <v>70.83871826666667</v>
+        <v>70.53241156666668</v>
       </c>
       <c r="O54">
-        <v>17.66717633570667</v>
+        <v>17.59078344472667</v>
       </c>
       <c r="P54">
-        <v>53.17154193096</v>
+        <v>52.94162812194001</v>
       </c>
       <c r="Q54">
-        <v>61.57154193096</v>
+        <v>61.34162812194001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1152120647008419</v>
+        <v>0.1164857750964206</v>
       </c>
       <c r="T54">
-        <v>1.603049993091038</v>
+        <v>1.632465937561677</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.447447749558673</v>
+        <v>5.344665716548132</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07674764969531768</v>
+        <v>0.07660925473423123</v>
       </c>
       <c r="C55">
-        <v>275.7285724528091</v>
+        <v>272.2384545939657</v>
       </c>
       <c r="D55">
-        <v>551.6955724528091</v>
+        <v>553.7444545939657</v>
       </c>
       <c r="E55">
-        <v>3.66700000000003</v>
+        <v>9.206000000000017</v>
       </c>
       <c r="F55">
-        <v>293.567</v>
+        <v>299.106</v>
       </c>
       <c r="G55">
         <v>17.6</v>
@@ -5785,28 +5785,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M55">
-        <v>16.2342551</v>
+        <v>16.5405618</v>
       </c>
       <c r="N55">
-        <v>70.53241156666668</v>
+        <v>70.22610486666667</v>
       </c>
       <c r="O55">
-        <v>17.59078344472667</v>
+        <v>17.51439055374667</v>
       </c>
       <c r="P55">
-        <v>52.94162812194001</v>
+        <v>52.71171431292001</v>
       </c>
       <c r="Q55">
-        <v>61.34162812194001</v>
+        <v>61.11171431292001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1164857750964206</v>
+        <v>0.1178148642048505</v>
       </c>
       <c r="T55">
-        <v>1.632465937561677</v>
+        <v>1.663160836139735</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.344665716548132</v>
+        <v>5.245690425500945</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07660925473423123</v>
+        <v>0.07647085977314479</v>
       </c>
       <c r="C56">
-        <v>272.2384545939657</v>
+        <v>268.7636117039426</v>
       </c>
       <c r="D56">
-        <v>553.7444545939657</v>
+        <v>555.8086117039426</v>
       </c>
       <c r="E56">
-        <v>9.206000000000017</v>
+        <v>14.74500000000006</v>
       </c>
       <c r="F56">
-        <v>299.106</v>
+        <v>304.645</v>
       </c>
       <c r="G56">
         <v>17.6</v>
@@ -5867,28 +5867,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M56">
-        <v>16.5405618</v>
+        <v>16.8468685</v>
       </c>
       <c r="N56">
-        <v>70.22610486666667</v>
+        <v>69.91979816666668</v>
       </c>
       <c r="O56">
-        <v>17.51439055374667</v>
+        <v>17.43799766276667</v>
       </c>
       <c r="P56">
-        <v>52.71171431292001</v>
+        <v>52.48180050390001</v>
       </c>
       <c r="Q56">
-        <v>61.11171431292001</v>
+        <v>60.88180050390001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1178148642048505</v>
+        <v>0.1192030239403218</v>
       </c>
       <c r="T56">
-        <v>1.663160836139735</v>
+        <v>1.695219952432373</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.245690425500945</v>
+        <v>5.150314235946382</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07647085977314479</v>
+        <v>0.07633246481205833</v>
       </c>
       <c r="C57">
-        <v>268.7636117039426</v>
+        <v>265.3042152403885</v>
       </c>
       <c r="D57">
-        <v>555.8086117039426</v>
+        <v>557.8882152403885</v>
       </c>
       <c r="E57">
-        <v>14.74500000000006</v>
+        <v>20.28400000000005</v>
       </c>
       <c r="F57">
-        <v>304.645</v>
+        <v>310.184</v>
       </c>
       <c r="G57">
         <v>17.6</v>
@@ -5949,28 +5949,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M57">
-        <v>16.8468685</v>
+        <v>17.1531752</v>
       </c>
       <c r="N57">
-        <v>69.91979816666668</v>
+        <v>69.61349146666667</v>
       </c>
       <c r="O57">
-        <v>17.43799766276667</v>
+        <v>17.36160477178667</v>
       </c>
       <c r="P57">
-        <v>52.48180050390001</v>
+        <v>52.25188669488</v>
       </c>
       <c r="Q57">
-        <v>60.88180050390001</v>
+        <v>60.65188669488</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1192030239403218</v>
+        <v>0.1206542818455871</v>
       </c>
       <c r="T57">
-        <v>1.695219952432373</v>
+        <v>1.728736301283768</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.150314235946382</v>
+        <v>5.05834433887591</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07633246481205833</v>
+        <v>0.07619406985097187</v>
       </c>
       <c r="C58">
-        <v>265.3042152403885</v>
+        <v>261.8604392366802</v>
       </c>
       <c r="D58">
-        <v>557.8882152403885</v>
+        <v>559.9834392366802</v>
       </c>
       <c r="E58">
-        <v>20.28400000000005</v>
+        <v>25.82300000000004</v>
       </c>
       <c r="F58">
-        <v>310.184</v>
+        <v>315.723</v>
       </c>
       <c r="G58">
         <v>17.6</v>
@@ -6031,28 +6031,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M58">
-        <v>17.1531752</v>
+        <v>17.4594819</v>
       </c>
       <c r="N58">
-        <v>69.61349146666667</v>
+        <v>69.30718476666668</v>
       </c>
       <c r="O58">
-        <v>17.36160477178667</v>
+        <v>17.28521188080667</v>
       </c>
       <c r="P58">
-        <v>52.25188669488</v>
+        <v>52.02197288586001</v>
       </c>
       <c r="Q58">
-        <v>60.65188669488</v>
+        <v>60.42197288586001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1206542818455871</v>
+        <v>0.1221730401185392</v>
       </c>
       <c r="T58">
-        <v>1.728736301283768</v>
+        <v>1.763811550081738</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.05834433887591</v>
+        <v>4.969601455737738</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07619406985097187</v>
+        <v>0.07605567488988542</v>
       </c>
       <c r="C59">
-        <v>261.8604392366802</v>
+        <v>258.4324603504735</v>
       </c>
       <c r="D59">
-        <v>559.9834392366802</v>
+        <v>562.0944603504735</v>
       </c>
       <c r="E59">
-        <v>25.82300000000004</v>
+        <v>31.36200000000002</v>
       </c>
       <c r="F59">
-        <v>315.723</v>
+        <v>321.262</v>
       </c>
       <c r="G59">
         <v>17.6</v>
@@ -6113,28 +6113,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M59">
-        <v>17.4594819</v>
+        <v>17.7657886</v>
       </c>
       <c r="N59">
-        <v>69.30718476666668</v>
+        <v>69.00087806666667</v>
       </c>
       <c r="O59">
-        <v>17.28521188080667</v>
+        <v>17.20881898982667</v>
       </c>
       <c r="P59">
-        <v>52.02197288586001</v>
+        <v>51.79205907684</v>
       </c>
       <c r="Q59">
-        <v>60.42197288586001</v>
+        <v>60.19205907684</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1221730401185392</v>
+        <v>0.1237641202140129</v>
       </c>
       <c r="T59">
-        <v>1.763811550081738</v>
+        <v>1.80055704882247</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.969601455737738</v>
+        <v>4.883918672018121</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07605567488988543</v>
+        <v>0.07591727992879899</v>
       </c>
       <c r="C60">
-        <v>258.4324603504732</v>
+        <v>255.0204579133544</v>
       </c>
       <c r="D60">
-        <v>562.0944603504731</v>
+        <v>564.2214579133544</v>
       </c>
       <c r="E60">
-        <v>31.36199999999997</v>
+        <v>36.90100000000001</v>
       </c>
       <c r="F60">
-        <v>321.2619999999999</v>
+        <v>326.801</v>
       </c>
       <c r="G60">
         <v>17.6</v>
@@ -6195,28 +6195,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M60">
-        <v>17.7657886</v>
+        <v>18.0720953</v>
       </c>
       <c r="N60">
-        <v>69.00087806666669</v>
+        <v>68.69457136666668</v>
       </c>
       <c r="O60">
-        <v>17.20881898982667</v>
+        <v>17.13242609884667</v>
       </c>
       <c r="P60">
-        <v>51.79205907684002</v>
+        <v>51.56214526782001</v>
       </c>
       <c r="Q60">
-        <v>60.19205907684002</v>
+        <v>59.96214526782001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1237641202140129</v>
+        <v>0.1254328139726804</v>
       </c>
       <c r="T60">
-        <v>1.80055704882247</v>
+        <v>1.839095010916407</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.883918672018122</v>
+        <v>4.801140389441542</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07591727992879899</v>
+        <v>0.07577888496771253</v>
       </c>
       <c r="C61">
-        <v>255.0204579133544</v>
+        <v>251.6246139816247</v>
       </c>
       <c r="D61">
-        <v>564.2214579133544</v>
+        <v>566.3646139816246</v>
       </c>
       <c r="E61">
-        <v>36.90100000000001</v>
+        <v>42.44</v>
       </c>
       <c r="F61">
-        <v>326.801</v>
+        <v>332.34</v>
       </c>
       <c r="G61">
         <v>17.6</v>
@@ -6277,28 +6277,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M61">
-        <v>18.0720953</v>
+        <v>18.378402</v>
       </c>
       <c r="N61">
-        <v>68.69457136666668</v>
+        <v>68.38826466666669</v>
       </c>
       <c r="O61">
-        <v>17.13242609884667</v>
+        <v>17.05603320786667</v>
       </c>
       <c r="P61">
-        <v>51.56214526782001</v>
+        <v>51.33223145880001</v>
       </c>
       <c r="Q61">
-        <v>59.96214526782001</v>
+        <v>59.73223145880001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1254328139726804</v>
+        <v>0.1271849424192813</v>
       </c>
       <c r="T61">
-        <v>1.839095010916407</v>
+        <v>1.879559871115042</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.801140389441542</v>
+        <v>4.721121382950852</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07577888496771253</v>
+        <v>0.07564049000662607</v>
       </c>
       <c r="C62">
-        <v>251.6246139816247</v>
+        <v>248.2451133882444</v>
       </c>
       <c r="D62">
-        <v>566.3646139816246</v>
+        <v>568.5241133882444</v>
       </c>
       <c r="E62">
-        <v>42.44</v>
+        <v>47.97899999999998</v>
       </c>
       <c r="F62">
-        <v>332.34</v>
+        <v>337.879</v>
       </c>
       <c r="G62">
         <v>17.6</v>
@@ -6359,28 +6359,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M62">
-        <v>18.378402</v>
+        <v>18.6847087</v>
       </c>
       <c r="N62">
-        <v>68.38826466666669</v>
+        <v>68.08195796666668</v>
       </c>
       <c r="O62">
-        <v>17.05603320786667</v>
+        <v>16.97964031688667</v>
       </c>
       <c r="P62">
-        <v>51.33223145880001</v>
+        <v>51.10231764978001</v>
       </c>
       <c r="Q62">
-        <v>59.73223145880001</v>
+        <v>59.50231764978</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1271849424192813</v>
+        <v>0.1290269236067335</v>
       </c>
       <c r="T62">
-        <v>1.879559871115042</v>
+        <v>1.922099852349504</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.721121382950852</v>
+        <v>4.64372595044346</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07564049000662607</v>
+        <v>0.07550209504553962</v>
       </c>
       <c r="C63">
-        <v>248.2451133882444</v>
+        <v>244.8821437959721</v>
       </c>
       <c r="D63">
-        <v>568.5241133882444</v>
+        <v>570.7001437959721</v>
       </c>
       <c r="E63">
-        <v>47.97899999999998</v>
+        <v>53.51800000000003</v>
       </c>
       <c r="F63">
-        <v>337.879</v>
+        <v>343.418</v>
       </c>
       <c r="G63">
         <v>17.6</v>
@@ -6441,28 +6441,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M63">
-        <v>18.6847087</v>
+        <v>18.9910154</v>
       </c>
       <c r="N63">
-        <v>68.08195796666668</v>
+        <v>67.77565126666667</v>
       </c>
       <c r="O63">
-        <v>16.97964031688667</v>
+        <v>16.90324742590667</v>
       </c>
       <c r="P63">
-        <v>51.10231764978001</v>
+        <v>50.87240384076</v>
       </c>
       <c r="Q63">
-        <v>59.50231764978</v>
+        <v>59.27240384076</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1290269236067335</v>
+        <v>0.1309658511724727</v>
       </c>
       <c r="T63">
-        <v>1.922099852349504</v>
+        <v>1.966878779964728</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.64372595044346</v>
+        <v>4.568827144791145</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07550209504553962</v>
+        <v>0.07654589508445317</v>
       </c>
       <c r="C64">
-        <v>244.8821437959721</v>
+        <v>223.3305559980181</v>
       </c>
       <c r="D64">
-        <v>570.7001437959721</v>
+        <v>554.6875559980181</v>
       </c>
       <c r="E64">
-        <v>53.51800000000003</v>
+        <v>59.05700000000002</v>
       </c>
       <c r="F64">
-        <v>343.418</v>
+        <v>348.957</v>
       </c>
       <c r="G64">
         <v>17.6</v>
@@ -6523,45 +6523,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M64">
-        <v>18.9910154</v>
+        <v>20.1697146</v>
       </c>
       <c r="N64">
-        <v>67.77565126666667</v>
+        <v>66.59695206666667</v>
       </c>
       <c r="O64">
-        <v>16.90324742590667</v>
+        <v>16.60927984542667</v>
       </c>
       <c r="P64">
-        <v>50.87240384076</v>
+        <v>49.98767222124</v>
       </c>
       <c r="Q64">
-        <v>59.27240384076</v>
+        <v>58.38767222124</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1309658511724727</v>
+        <v>0.1330095856336572</v>
       </c>
       <c r="T64">
-        <v>1.966878779964728</v>
+        <v>2.014078190153747</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.568827144791145</v>
+        <v>4.301829172469633</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07654589508445317</v>
+        <v>0.07642626512336673</v>
       </c>
       <c r="C65">
-        <v>223.3305559980181</v>
+        <v>219.5810219145928</v>
       </c>
       <c r="D65">
-        <v>554.6875559980181</v>
+        <v>556.4770219145928</v>
       </c>
       <c r="E65">
-        <v>59.05700000000002</v>
+        <v>64.596</v>
       </c>
       <c r="F65">
-        <v>348.957</v>
+        <v>354.496</v>
       </c>
       <c r="G65">
         <v>17.6</v>
@@ -6605,28 +6605,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M65">
-        <v>20.1697146</v>
+        <v>20.4898688</v>
       </c>
       <c r="N65">
-        <v>66.59695206666667</v>
+        <v>66.27679786666668</v>
       </c>
       <c r="O65">
-        <v>16.60927984542667</v>
+        <v>16.52943338794667</v>
       </c>
       <c r="P65">
-        <v>49.98767222124</v>
+        <v>49.74736447872002</v>
       </c>
       <c r="Q65">
-        <v>58.38767222124</v>
+        <v>58.14736447872001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1330095856336572</v>
+        <v>0.1351668608982409</v>
       </c>
       <c r="T65">
-        <v>2.014078190153747</v>
+        <v>2.063899789797711</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.301829172469633</v>
+        <v>4.234613091649795</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07642626512336673</v>
+        <v>0.07630663516228027</v>
       </c>
       <c r="C66">
-        <v>219.5810219145928</v>
+        <v>215.8430711168547</v>
       </c>
       <c r="D66">
-        <v>556.4770219145928</v>
+        <v>558.2780711168547</v>
       </c>
       <c r="E66">
-        <v>64.596</v>
+        <v>70.13500000000005</v>
       </c>
       <c r="F66">
-        <v>354.496</v>
+        <v>360.035</v>
       </c>
       <c r="G66">
         <v>17.6</v>
@@ -6687,28 +6687,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M66">
-        <v>20.4898688</v>
+        <v>20.810023</v>
       </c>
       <c r="N66">
-        <v>66.27679786666668</v>
+        <v>65.95664366666668</v>
       </c>
       <c r="O66">
-        <v>16.52943338794667</v>
+        <v>16.44958693046667</v>
       </c>
       <c r="P66">
-        <v>49.74736447872002</v>
+        <v>49.50705673620001</v>
       </c>
       <c r="Q66">
-        <v>58.14736447872001</v>
+        <v>57.90705673620001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1351668608982409</v>
+        <v>0.1374474090350865</v>
       </c>
       <c r="T66">
-        <v>2.063899789797711</v>
+        <v>2.11656833799276</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.234613091649795</v>
+        <v>4.169465197932105</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07630663516228027</v>
+        <v>0.07618700520119381</v>
       </c>
       <c r="C67">
-        <v>215.8430711168547</v>
+        <v>212.1168164386117</v>
       </c>
       <c r="D67">
-        <v>558.2780711168547</v>
+        <v>560.0908164386117</v>
       </c>
       <c r="E67">
-        <v>70.13500000000005</v>
+        <v>75.67400000000004</v>
       </c>
       <c r="F67">
-        <v>360.035</v>
+        <v>365.574</v>
       </c>
       <c r="G67">
         <v>17.6</v>
@@ -6769,28 +6769,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M67">
-        <v>20.810023</v>
+        <v>21.1301772</v>
       </c>
       <c r="N67">
-        <v>65.95664366666668</v>
+        <v>65.63648946666667</v>
       </c>
       <c r="O67">
-        <v>16.44958693046667</v>
+        <v>16.36974047298667</v>
       </c>
       <c r="P67">
-        <v>49.50705673620001</v>
+        <v>49.26674899368</v>
       </c>
       <c r="Q67">
-        <v>57.90705673620001</v>
+        <v>57.66674899368</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1374474090350865</v>
+        <v>0.1398621070623348</v>
       </c>
       <c r="T67">
-        <v>2.11656833799276</v>
+        <v>2.172335036081634</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.169465197932105</v>
+        <v>4.106291482811923</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07618700520119381</v>
+        <v>0.07606737524010737</v>
       </c>
       <c r="C68">
-        <v>212.1168164386117</v>
+        <v>208.4023721839447</v>
       </c>
       <c r="D68">
-        <v>560.0908164386117</v>
+        <v>561.9153721839447</v>
       </c>
       <c r="E68">
-        <v>75.67400000000004</v>
+        <v>81.21300000000002</v>
       </c>
       <c r="F68">
-        <v>365.574</v>
+        <v>371.113</v>
       </c>
       <c r="G68">
         <v>17.6</v>
@@ -6851,28 +6851,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M68">
-        <v>21.1301772</v>
+        <v>21.4503314</v>
       </c>
       <c r="N68">
-        <v>65.63648946666667</v>
+        <v>65.31633526666667</v>
       </c>
       <c r="O68">
-        <v>16.36974047298667</v>
+        <v>16.28989401550667</v>
       </c>
       <c r="P68">
-        <v>49.26674899368</v>
+        <v>49.02644125116</v>
       </c>
       <c r="Q68">
-        <v>57.66674899368</v>
+        <v>57.42644125116</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1398621070623348</v>
+        <v>0.1424231504245678</v>
       </c>
       <c r="T68">
-        <v>2.172335036081634</v>
+        <v>2.231481534054684</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.106291482811923</v>
+        <v>4.045003550232639</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07606737524010737</v>
+        <v>0.07773417327902089</v>
       </c>
       <c r="C69">
-        <v>208.4023721839447</v>
+        <v>178.4664478964087</v>
       </c>
       <c r="D69">
-        <v>561.9153721839447</v>
+        <v>537.5184478964087</v>
       </c>
       <c r="E69">
-        <v>81.21300000000002</v>
+        <v>86.75200000000001</v>
       </c>
       <c r="F69">
-        <v>371.113</v>
+        <v>376.652</v>
       </c>
       <c r="G69">
         <v>17.6</v>
@@ -6933,45 +6933,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M69">
-        <v>21.4503314</v>
+        <v>23.0887676</v>
       </c>
       <c r="N69">
-        <v>65.31633526666667</v>
+        <v>63.67789906666668</v>
       </c>
       <c r="O69">
-        <v>16.28989401550667</v>
+        <v>15.88126802722667</v>
       </c>
       <c r="P69">
-        <v>49.02644125116</v>
+        <v>47.79663103944002</v>
       </c>
       <c r="Q69">
-        <v>57.42644125116</v>
+        <v>56.19663103944001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1424231504245678</v>
+        <v>0.1451442589969403</v>
       </c>
       <c r="T69">
-        <v>2.231481534054684</v>
+        <v>2.294324688151048</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.045003550232639</v>
+        <v>3.757960068283016</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07773417327902089</v>
+        <v>0.07764081431793446</v>
       </c>
       <c r="C70">
-        <v>178.4664478964087</v>
+        <v>174.2377999539726</v>
       </c>
       <c r="D70">
-        <v>537.5184478964087</v>
+        <v>538.8287999539726</v>
       </c>
       <c r="E70">
-        <v>86.75200000000001</v>
+        <v>92.29100000000005</v>
       </c>
       <c r="F70">
-        <v>376.652</v>
+        <v>382.191</v>
       </c>
       <c r="G70">
         <v>17.6</v>
@@ -7015,28 +7015,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M70">
-        <v>23.0887676</v>
+        <v>23.4283083</v>
       </c>
       <c r="N70">
-        <v>63.67789906666668</v>
+        <v>63.33835836666668</v>
       </c>
       <c r="O70">
-        <v>15.88126802722667</v>
+        <v>15.79658657664667</v>
       </c>
       <c r="P70">
-        <v>47.79663103944002</v>
+        <v>47.54177179002001</v>
       </c>
       <c r="Q70">
-        <v>56.19663103944001</v>
+        <v>55.94177179002001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1451442589969403</v>
+        <v>0.1480409229610789</v>
       </c>
       <c r="T70">
-        <v>2.294324688151048</v>
+        <v>2.361222239285888</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.757960068283016</v>
+        <v>3.70349687888761</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07764081431793446</v>
+        <v>0.07754745535684801</v>
       </c>
       <c r="C71">
-        <v>174.2377999539726</v>
+        <v>170.0155563255636</v>
       </c>
       <c r="D71">
-        <v>538.8287999539726</v>
+        <v>540.1455563255636</v>
       </c>
       <c r="E71">
-        <v>92.29100000000005</v>
+        <v>97.83000000000004</v>
       </c>
       <c r="F71">
-        <v>382.191</v>
+        <v>387.73</v>
       </c>
       <c r="G71">
         <v>17.6</v>
@@ -7097,28 +7097,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M71">
-        <v>23.4283083</v>
+        <v>23.767849</v>
       </c>
       <c r="N71">
-        <v>63.33835836666668</v>
+        <v>62.99881766666668</v>
       </c>
       <c r="O71">
-        <v>15.79658657664667</v>
+        <v>15.71190512606667</v>
       </c>
       <c r="P71">
-        <v>47.54177179002001</v>
+        <v>47.28691254060001</v>
       </c>
       <c r="Q71">
-        <v>55.94177179002001</v>
+        <v>55.68691254060001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1480409229610789</v>
+        <v>0.15113069785616</v>
       </c>
       <c r="T71">
-        <v>2.361222239285888</v>
+        <v>2.43257962716305</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.70349687888761</v>
+        <v>3.650589780617786</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07754745535684801</v>
+        <v>0.07745409639576156</v>
       </c>
       <c r="C72">
-        <v>170.0155563255636</v>
+        <v>165.7997640775945</v>
       </c>
       <c r="D72">
-        <v>540.1455563255636</v>
+        <v>541.4687640775945</v>
       </c>
       <c r="E72">
-        <v>97.83000000000004</v>
+        <v>103.369</v>
       </c>
       <c r="F72">
-        <v>387.73</v>
+        <v>393.269</v>
       </c>
       <c r="G72">
         <v>17.6</v>
@@ -7179,28 +7179,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M72">
-        <v>23.767849</v>
+        <v>24.1073897</v>
       </c>
       <c r="N72">
-        <v>62.99881766666668</v>
+        <v>62.65927696666668</v>
       </c>
       <c r="O72">
-        <v>15.71190512606667</v>
+        <v>15.62722367548667</v>
       </c>
       <c r="P72">
-        <v>47.28691254060001</v>
+        <v>47.03205329118001</v>
       </c>
       <c r="Q72">
-        <v>55.68691254060001</v>
+        <v>55.43205329118</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.15113069785616</v>
+        <v>0.1544335606750399</v>
       </c>
       <c r="T72">
-        <v>2.43257962716305</v>
+        <v>2.508858214204155</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.650589780617786</v>
+        <v>3.599173023144297</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07745409639576156</v>
+        <v>0.0773607374346751</v>
       </c>
       <c r="C73">
-        <v>165.7997640775946</v>
+        <v>161.5904707388105</v>
       </c>
       <c r="D73">
-        <v>541.4687640775945</v>
+        <v>542.7984707388105</v>
       </c>
       <c r="E73">
-        <v>103.369</v>
+        <v>108.908</v>
       </c>
       <c r="F73">
-        <v>393.2689999999999</v>
+        <v>398.808</v>
       </c>
       <c r="G73">
         <v>17.6</v>
@@ -7261,28 +7261,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M73">
-        <v>24.1073897</v>
+        <v>24.4469304</v>
       </c>
       <c r="N73">
-        <v>62.65927696666668</v>
+        <v>62.31973626666668</v>
       </c>
       <c r="O73">
-        <v>15.62722367548667</v>
+        <v>15.54254222490667</v>
       </c>
       <c r="P73">
-        <v>47.03205329118001</v>
+        <v>46.77719404176001</v>
       </c>
       <c r="Q73">
-        <v>55.43205329118</v>
+        <v>55.17719404176001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1544335606750399</v>
+        <v>0.1579723422666968</v>
       </c>
       <c r="T73">
-        <v>2.508858214204154</v>
+        <v>2.590585271748195</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.599173023144297</v>
+        <v>3.549184508933959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0773607374346751</v>
+        <v>0.07726737847358864</v>
       </c>
       <c r="C74">
-        <v>161.5904707388105</v>
+        <v>157.3877243059779</v>
       </c>
       <c r="D74">
-        <v>542.7984707388105</v>
+        <v>544.1347243059779</v>
       </c>
       <c r="E74">
-        <v>108.908</v>
+        <v>114.447</v>
       </c>
       <c r="F74">
-        <v>398.808</v>
+        <v>404.347</v>
       </c>
       <c r="G74">
         <v>17.6</v>
@@ -7343,28 +7343,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M74">
-        <v>24.4469304</v>
+        <v>24.7864711</v>
       </c>
       <c r="N74">
-        <v>62.31973626666668</v>
+        <v>61.98019556666668</v>
       </c>
       <c r="O74">
-        <v>15.54254222490667</v>
+        <v>15.45786077432667</v>
       </c>
       <c r="P74">
-        <v>46.77719404176001</v>
+        <v>46.52233479234001</v>
       </c>
       <c r="Q74">
-        <v>55.17719404176001</v>
+        <v>54.92233479234001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1579723422666968</v>
+        <v>0.1617732558281061</v>
       </c>
       <c r="T74">
-        <v>2.590585271748195</v>
+        <v>2.678366185406608</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.549184508933959</v>
+        <v>3.500565543058152</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07726737847358864</v>
+        <v>0.07872926271250219</v>
       </c>
       <c r="C75">
-        <v>157.3877243059779</v>
+        <v>131.651722524155</v>
       </c>
       <c r="D75">
-        <v>544.1347243059779</v>
+        <v>523.937722524155</v>
       </c>
       <c r="E75">
-        <v>114.447</v>
+        <v>119.986</v>
       </c>
       <c r="F75">
-        <v>404.347</v>
+        <v>409.886</v>
       </c>
       <c r="G75">
         <v>17.6</v>
@@ -7425,45 +7425,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M75">
-        <v>24.7864711</v>
+        <v>26.2736926</v>
       </c>
       <c r="N75">
-        <v>61.98019556666668</v>
+        <v>60.49297406666668</v>
       </c>
       <c r="O75">
-        <v>15.45786077432667</v>
+        <v>15.08694773222667</v>
       </c>
       <c r="P75">
-        <v>46.52233479234001</v>
+        <v>45.40602633444001</v>
       </c>
       <c r="Q75">
-        <v>54.92233479234001</v>
+        <v>53.80602633444001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1617732558281061</v>
+        <v>0.1658665473557777</v>
       </c>
       <c r="T75">
-        <v>2.678366185406608</v>
+        <v>2.772899477038746</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.500565543058152</v>
+        <v>3.302416146357238</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07872926271250219</v>
+        <v>0.07865692055141574</v>
       </c>
       <c r="C76">
-        <v>131.651722524155</v>
+        <v>127.0768557837816</v>
       </c>
       <c r="D76">
-        <v>523.937722524155</v>
+        <v>524.9018557837816</v>
       </c>
       <c r="E76">
-        <v>119.986</v>
+        <v>125.525</v>
       </c>
       <c r="F76">
-        <v>409.886</v>
+        <v>415.425</v>
       </c>
       <c r="G76">
         <v>17.6</v>
@@ -7507,28 +7507,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M76">
-        <v>26.2736926</v>
+        <v>26.6287425</v>
       </c>
       <c r="N76">
-        <v>60.49297406666668</v>
+        <v>60.13792416666668</v>
       </c>
       <c r="O76">
-        <v>15.08694773222667</v>
+        <v>14.99839828716667</v>
       </c>
       <c r="P76">
-        <v>45.40602633444001</v>
+        <v>45.13952587950001</v>
       </c>
       <c r="Q76">
-        <v>53.80602633444001</v>
+        <v>53.5395258795</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1658665473557777</v>
+        <v>0.170287302205663</v>
       </c>
       <c r="T76">
-        <v>2.772899477038746</v>
+        <v>2.874995432001455</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.302416146357238</v>
+        <v>3.258383931072475</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07865692055141574</v>
+        <v>0.0785845783903293</v>
       </c>
       <c r="C77">
-        <v>127.0768557837816</v>
+        <v>122.5055439186881</v>
       </c>
       <c r="D77">
-        <v>524.9018557837816</v>
+        <v>525.8695439186881</v>
       </c>
       <c r="E77">
-        <v>125.525</v>
+        <v>131.064</v>
       </c>
       <c r="F77">
-        <v>415.425</v>
+        <v>420.964</v>
       </c>
       <c r="G77">
         <v>17.6</v>
@@ -7589,28 +7589,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M77">
-        <v>26.6287425</v>
+        <v>26.9837924</v>
       </c>
       <c r="N77">
-        <v>60.13792416666668</v>
+        <v>59.78287426666668</v>
       </c>
       <c r="O77">
-        <v>14.99839828716667</v>
+        <v>14.90984884210667</v>
       </c>
       <c r="P77">
-        <v>45.13952587950001</v>
+        <v>44.87302542456001</v>
       </c>
       <c r="Q77">
-        <v>53.5395258795</v>
+        <v>53.27302542456001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.170287302205663</v>
+        <v>0.1750764532930388</v>
       </c>
       <c r="T77">
-        <v>2.874995432001455</v>
+        <v>2.985599383211057</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.258383931072475</v>
+        <v>3.215510458295205</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0785845783903293</v>
+        <v>0.07851223622924283</v>
       </c>
       <c r="C78">
-        <v>122.5055439186881</v>
+        <v>117.9378066260671</v>
       </c>
       <c r="D78">
-        <v>525.8695439186881</v>
+        <v>526.8408066260671</v>
       </c>
       <c r="E78">
-        <v>131.064</v>
+        <v>136.603</v>
       </c>
       <c r="F78">
-        <v>420.964</v>
+        <v>426.503</v>
       </c>
       <c r="G78">
         <v>17.6</v>
@@ -7671,28 +7671,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M78">
-        <v>26.9837924</v>
+        <v>27.3388423</v>
       </c>
       <c r="N78">
-        <v>59.78287426666668</v>
+        <v>59.42782436666668</v>
       </c>
       <c r="O78">
-        <v>14.90984884210667</v>
+        <v>14.82129939704667</v>
       </c>
       <c r="P78">
-        <v>44.87302542456001</v>
+        <v>44.60652496962001</v>
       </c>
       <c r="Q78">
-        <v>53.27302542456001</v>
+        <v>53.00652496962001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1750764532930388</v>
+        <v>0.1802820523010558</v>
       </c>
       <c r="T78">
-        <v>2.985599383211057</v>
+        <v>3.10582106930845</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.215510458295205</v>
+        <v>3.17375058221345</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07851223622924283</v>
+        <v>0.07843989406815638</v>
       </c>
       <c r="C79">
-        <v>117.9378066260671</v>
+        <v>113.3736637488993</v>
       </c>
       <c r="D79">
-        <v>526.8408066260671</v>
+        <v>527.8156637488993</v>
       </c>
       <c r="E79">
-        <v>136.603</v>
+        <v>142.142</v>
       </c>
       <c r="F79">
-        <v>426.503</v>
+        <v>432.042</v>
       </c>
       <c r="G79">
         <v>17.6</v>
@@ -7753,28 +7753,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M79">
-        <v>27.3388423</v>
+        <v>27.6938922</v>
       </c>
       <c r="N79">
-        <v>59.42782436666668</v>
+        <v>59.07277446666668</v>
       </c>
       <c r="O79">
-        <v>14.82129939704667</v>
+        <v>14.73274995198667</v>
       </c>
       <c r="P79">
-        <v>44.60652496962001</v>
+        <v>44.34002451468001</v>
       </c>
       <c r="Q79">
-        <v>53.00652496962001</v>
+        <v>52.74002451468001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1802820523010558</v>
+        <v>0.1859608875825291</v>
       </c>
       <c r="T79">
-        <v>3.10582106930845</v>
+        <v>3.236971999596515</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.17375058221345</v>
+        <v>3.133061472185072</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07843989406815638</v>
+        <v>0.07836755190706994</v>
       </c>
       <c r="C80">
-        <v>113.3736637488993</v>
+        <v>108.813135277307</v>
       </c>
       <c r="D80">
-        <v>527.8156637488993</v>
+        <v>528.794135277307</v>
       </c>
       <c r="E80">
-        <v>142.142</v>
+        <v>147.681</v>
       </c>
       <c r="F80">
-        <v>432.042</v>
+        <v>437.581</v>
       </c>
       <c r="G80">
         <v>17.6</v>
@@ -7835,28 +7835,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M80">
-        <v>27.6938922</v>
+        <v>28.0489421</v>
       </c>
       <c r="N80">
-        <v>59.07277446666668</v>
+        <v>58.71772456666667</v>
       </c>
       <c r="O80">
-        <v>14.73274995198667</v>
+        <v>14.64420050692667</v>
       </c>
       <c r="P80">
-        <v>44.34002451468001</v>
+        <v>44.07352405974001</v>
       </c>
       <c r="Q80">
-        <v>52.74002451468001</v>
+        <v>52.47352405974001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1859608875825291</v>
+        <v>0.1921805643193807</v>
       </c>
       <c r="T80">
-        <v>3.236971999596515</v>
+        <v>3.38061349467392</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.133061472185072</v>
+        <v>3.093402466208045</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07836755190706994</v>
+        <v>0.0782952097459835</v>
       </c>
       <c r="C81">
-        <v>108.813135277307</v>
+        <v>104.2562413499194</v>
       </c>
       <c r="D81">
-        <v>528.794135277307</v>
+        <v>529.7762413499194</v>
       </c>
       <c r="E81">
-        <v>147.681</v>
+        <v>153.22</v>
       </c>
       <c r="F81">
-        <v>437.581</v>
+        <v>443.12</v>
       </c>
       <c r="G81">
         <v>17.6</v>
@@ -7917,28 +7917,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M81">
-        <v>28.0489421</v>
+        <v>28.403992</v>
       </c>
       <c r="N81">
-        <v>58.71772456666667</v>
+        <v>58.36267466666668</v>
       </c>
       <c r="O81">
-        <v>14.64420050692667</v>
+        <v>14.55565106186667</v>
       </c>
       <c r="P81">
-        <v>44.07352405974001</v>
+        <v>43.80702360480001</v>
       </c>
       <c r="Q81">
-        <v>52.47352405974001</v>
+        <v>52.20702360480001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1921805643193807</v>
+        <v>0.1990222087299175</v>
       </c>
       <c r="T81">
-        <v>3.38061349467392</v>
+        <v>3.538619139259065</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.093402466208045</v>
+        <v>3.054734935380445</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0782952097459835</v>
+        <v>0.07822286758489702</v>
       </c>
       <c r="C82">
-        <v>104.2562413499194</v>
+        <v>99.703002255255</v>
       </c>
       <c r="D82">
-        <v>529.7762413499194</v>
+        <v>530.762002255255</v>
       </c>
       <c r="E82">
-        <v>153.22</v>
+        <v>158.759</v>
       </c>
       <c r="F82">
-        <v>443.12</v>
+        <v>448.659</v>
       </c>
       <c r="G82">
         <v>17.6</v>
@@ -7999,28 +7999,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M82">
-        <v>28.403992</v>
+        <v>28.7590419</v>
       </c>
       <c r="N82">
-        <v>58.36267466666668</v>
+        <v>58.00762476666668</v>
       </c>
       <c r="O82">
-        <v>14.55565106186667</v>
+        <v>14.46710161680667</v>
       </c>
       <c r="P82">
-        <v>43.80702360480001</v>
+        <v>43.54052314986001</v>
       </c>
       <c r="Q82">
-        <v>52.20702360480001</v>
+        <v>51.94052314986001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1990222087299175</v>
+        <v>0.2065840262363002</v>
       </c>
       <c r="T82">
-        <v>3.538619139259065</v>
+        <v>3.713256956958435</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.054734935380445</v>
+        <v>3.01702215840044</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07822286758489702</v>
+        <v>0.08295136302381059</v>
       </c>
       <c r="C83">
-        <v>99.703002255255</v>
+        <v>36.61151738050739</v>
       </c>
       <c r="D83">
-        <v>530.762002255255</v>
+        <v>473.2095173805074</v>
       </c>
       <c r="E83">
-        <v>158.759</v>
+        <v>164.2980000000001</v>
       </c>
       <c r="F83">
-        <v>448.659</v>
+        <v>454.198</v>
       </c>
       <c r="G83">
         <v>17.6</v>
@@ -8081,45 +8081,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M83">
-        <v>28.7590419</v>
+        <v>32.65683620000001</v>
       </c>
       <c r="N83">
-        <v>58.00762476666668</v>
+        <v>54.10983046666667</v>
       </c>
       <c r="O83">
-        <v>14.46710161680667</v>
+        <v>13.49499171838667</v>
       </c>
       <c r="P83">
-        <v>43.54052314986001</v>
+        <v>40.61483874828001</v>
       </c>
       <c r="Q83">
-        <v>51.94052314986001</v>
+        <v>49.01483874828001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2065840262363002</v>
+        <v>0.2149860456878367</v>
       </c>
       <c r="T83">
-        <v>3.713256956958435</v>
+        <v>3.907298976624404</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.2494</v>
       </c>
       <c r="W83">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.01702215840044</v>
+        <v>2.656922003567102</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08295136302381059</v>
+        <v>0.08293756766272413</v>
       </c>
       <c r="C84">
-        <v>36.61151738050739</v>
+        <v>31.22226683091685</v>
       </c>
       <c r="D84">
-        <v>473.2095173805074</v>
+        <v>473.3592668309169</v>
       </c>
       <c r="E84">
-        <v>164.2980000000001</v>
+        <v>169.837</v>
       </c>
       <c r="F84">
-        <v>454.198</v>
+        <v>459.737</v>
       </c>
       <c r="G84">
         <v>17.6</v>
@@ -8163,28 +8163,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M84">
-        <v>32.65683620000001</v>
+        <v>33.0550903</v>
       </c>
       <c r="N84">
-        <v>54.10983046666667</v>
+        <v>53.71157636666668</v>
       </c>
       <c r="O84">
-        <v>13.49499171838667</v>
+        <v>13.39566714584667</v>
       </c>
       <c r="P84">
-        <v>40.61483874828001</v>
+        <v>40.31590922082</v>
       </c>
       <c r="Q84">
-        <v>49.01483874828001</v>
+        <v>48.71590922082</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2149860456878367</v>
+        <v>0.2243765380160244</v>
       </c>
       <c r="T84">
-        <v>3.907298976624404</v>
+        <v>4.12416946919225</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.656922003567102</v>
+        <v>2.62491089509039</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08293756766272413</v>
+        <v>0.08292377230163769</v>
       </c>
       <c r="C85">
-        <v>31.22226683091685</v>
+        <v>25.83311108921043</v>
       </c>
       <c r="D85">
-        <v>473.3592668309169</v>
+        <v>473.5091110892104</v>
       </c>
       <c r="E85">
-        <v>169.837</v>
+        <v>175.376</v>
       </c>
       <c r="F85">
-        <v>459.737</v>
+        <v>465.276</v>
       </c>
       <c r="G85">
         <v>17.6</v>
@@ -8245,28 +8245,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M85">
-        <v>33.0550903</v>
+        <v>33.45334440000001</v>
       </c>
       <c r="N85">
-        <v>53.71157636666668</v>
+        <v>53.31332226666667</v>
       </c>
       <c r="O85">
-        <v>13.39566714584667</v>
+        <v>13.29634257330667</v>
       </c>
       <c r="P85">
-        <v>40.31590922082</v>
+        <v>40.01697969336001</v>
       </c>
       <c r="Q85">
-        <v>48.71590922082</v>
+        <v>48.41697969336001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2243765380160244</v>
+        <v>0.2349408418852356</v>
       </c>
       <c r="T85">
-        <v>4.12416946919225</v>
+        <v>4.368148773331078</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.62491089509039</v>
+        <v>2.593661955863123</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08292377230163769</v>
+        <v>0.08290997694055123</v>
       </c>
       <c r="C86">
-        <v>25.83311108921049</v>
+        <v>20.44405024545296</v>
       </c>
       <c r="D86">
-        <v>473.5091110892104</v>
+        <v>473.6590502454529</v>
       </c>
       <c r="E86">
-        <v>175.376</v>
+        <v>180.915</v>
       </c>
       <c r="F86">
-        <v>465.276</v>
+        <v>470.8149999999999</v>
       </c>
       <c r="G86">
         <v>17.6</v>
@@ -8327,28 +8327,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M86">
-        <v>33.4533444</v>
+        <v>33.8515985</v>
       </c>
       <c r="N86">
-        <v>53.31332226666668</v>
+        <v>52.91506816666668</v>
       </c>
       <c r="O86">
-        <v>13.29634257330667</v>
+        <v>13.19701800076667</v>
       </c>
       <c r="P86">
-        <v>40.01697969336001</v>
+        <v>39.71805016590001</v>
       </c>
       <c r="Q86">
-        <v>48.41697969336001</v>
+        <v>48.11805016590001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2349408418852355</v>
+        <v>0.2469137196036748</v>
       </c>
       <c r="T86">
-        <v>4.368148773331074</v>
+        <v>4.644658651355078</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.593661955863124</v>
+        <v>2.563148285794146</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08290997694055123</v>
+        <v>0.08289618157946478</v>
       </c>
       <c r="C87">
-        <v>20.44405024545296</v>
+        <v>15.0550843898223</v>
       </c>
       <c r="D87">
-        <v>473.6590502454529</v>
+        <v>473.8090843898223</v>
       </c>
       <c r="E87">
-        <v>180.915</v>
+        <v>186.454</v>
       </c>
       <c r="F87">
-        <v>470.8149999999999</v>
+        <v>476.354</v>
       </c>
       <c r="G87">
         <v>17.6</v>
@@ -8409,28 +8409,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M87">
-        <v>33.8515985</v>
+        <v>34.2498526</v>
       </c>
       <c r="N87">
-        <v>52.91506816666668</v>
+        <v>52.51681406666668</v>
       </c>
       <c r="O87">
-        <v>13.19701800076667</v>
+        <v>13.09769342822667</v>
       </c>
       <c r="P87">
-        <v>39.71805016590001</v>
+        <v>39.41912063844001</v>
       </c>
       <c r="Q87">
-        <v>48.11805016590001</v>
+        <v>47.81912063844</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2469137196036748</v>
+        <v>0.2605970084247484</v>
       </c>
       <c r="T87">
-        <v>4.644658651355078</v>
+        <v>4.960669940525369</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.563148285794146</v>
+        <v>2.53334423595933</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08289618157946478</v>
+        <v>0.08288238621837832</v>
       </c>
       <c r="C88">
-        <v>15.0550843898223</v>
+        <v>9.666213612611557</v>
       </c>
       <c r="D88">
-        <v>473.8090843898223</v>
+        <v>473.9592136126115</v>
       </c>
       <c r="E88">
-        <v>186.454</v>
+        <v>191.993</v>
       </c>
       <c r="F88">
-        <v>476.354</v>
+        <v>481.893</v>
       </c>
       <c r="G88">
         <v>17.6</v>
@@ -8491,28 +8491,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M88">
-        <v>34.2498526</v>
+        <v>34.6481067</v>
       </c>
       <c r="N88">
-        <v>52.51681406666668</v>
+        <v>52.11855996666668</v>
       </c>
       <c r="O88">
-        <v>13.09769342822667</v>
+        <v>12.99836885568667</v>
       </c>
       <c r="P88">
-        <v>39.41912063844001</v>
+        <v>39.12019111098001</v>
       </c>
       <c r="Q88">
-        <v>47.81912063844</v>
+        <v>47.52019111098001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2605970084247484</v>
+        <v>0.2763854186029102</v>
       </c>
       <c r="T88">
-        <v>4.960669940525369</v>
+        <v>5.325298351106472</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.53334423595933</v>
+        <v>2.50422533669543</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08288238621837832</v>
+        <v>0.08544465005729188</v>
       </c>
       <c r="C89">
-        <v>9.666213612611557</v>
+        <v>-22.21539715961961</v>
       </c>
       <c r="D89">
-        <v>473.9592136126115</v>
+        <v>447.6166028403803</v>
       </c>
       <c r="E89">
-        <v>191.993</v>
+        <v>197.532</v>
       </c>
       <c r="F89">
-        <v>481.893</v>
+        <v>487.432</v>
       </c>
       <c r="G89">
         <v>17.6</v>
@@ -8573,45 +8573,45 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M89">
-        <v>34.6481067</v>
+        <v>36.9473456</v>
       </c>
       <c r="N89">
-        <v>52.11855996666668</v>
+        <v>49.81932106666668</v>
       </c>
       <c r="O89">
-        <v>12.99836885568667</v>
+        <v>12.42493867402667</v>
       </c>
       <c r="P89">
-        <v>39.12019111098001</v>
+        <v>37.39438239264001</v>
       </c>
       <c r="Q89">
-        <v>47.52019111098001</v>
+        <v>45.79438239264001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2763854186029102</v>
+        <v>0.2948052304774323</v>
       </c>
       <c r="T89">
-        <v>5.325298351106472</v>
+        <v>5.750698163451094</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.2494</v>
       </c>
       <c r="W89">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.50422533669543</v>
+        <v>2.348387015565922</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08544465005729188</v>
+        <v>0.08546012809620543</v>
       </c>
       <c r="C90">
-        <v>-22.21539715961961</v>
+        <v>-27.90463188603991</v>
       </c>
       <c r="D90">
-        <v>447.6166028403803</v>
+        <v>447.4663681139601</v>
       </c>
       <c r="E90">
-        <v>197.532</v>
+        <v>203.071</v>
       </c>
       <c r="F90">
-        <v>487.432</v>
+        <v>492.971</v>
       </c>
       <c r="G90">
         <v>17.6</v>
@@ -8655,28 +8655,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M90">
-        <v>36.9473456</v>
+        <v>37.3672018</v>
       </c>
       <c r="N90">
-        <v>49.81932106666668</v>
+        <v>49.39946486666668</v>
       </c>
       <c r="O90">
-        <v>12.42493867402667</v>
+        <v>12.32022653774667</v>
       </c>
       <c r="P90">
-        <v>37.39438239264001</v>
+        <v>37.07923832892001</v>
       </c>
       <c r="Q90">
-        <v>45.79438239264001</v>
+        <v>45.47923832892</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2948052304774323</v>
+        <v>0.316574099056413</v>
       </c>
       <c r="T90">
-        <v>5.750698163451094</v>
+        <v>6.25344339622201</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.348387015565922</v>
+        <v>2.322000644604506</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08546012809620543</v>
+        <v>0.08547560613511898</v>
       </c>
       <c r="C91">
-        <v>-27.90463188603991</v>
+        <v>-33.59376579895127</v>
       </c>
       <c r="D91">
-        <v>447.4663681139601</v>
+        <v>447.3162342010487</v>
       </c>
       <c r="E91">
-        <v>203.071</v>
+        <v>208.61</v>
       </c>
       <c r="F91">
-        <v>492.971</v>
+        <v>498.51</v>
       </c>
       <c r="G91">
         <v>17.6</v>
@@ -8737,28 +8737,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M91">
-        <v>37.3672018</v>
+        <v>37.787058</v>
       </c>
       <c r="N91">
-        <v>49.39946486666668</v>
+        <v>48.97960866666668</v>
       </c>
       <c r="O91">
-        <v>12.32022653774667</v>
+        <v>12.21551440146667</v>
       </c>
       <c r="P91">
-        <v>37.07923832892001</v>
+        <v>36.76409426520001</v>
       </c>
       <c r="Q91">
-        <v>45.47923832892</v>
+        <v>45.16409426520001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.316574099056413</v>
+        <v>0.3426967413511898</v>
       </c>
       <c r="T91">
-        <v>6.25344339622201</v>
+        <v>6.85673767554711</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.322000644604506</v>
+        <v>2.296200637442234</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08547560613511898</v>
+        <v>0.08549108417403252</v>
       </c>
       <c r="C92">
-        <v>-33.59376579895127</v>
+        <v>-39.28279899979447</v>
       </c>
       <c r="D92">
-        <v>447.3162342010487</v>
+        <v>447.1662010002055</v>
       </c>
       <c r="E92">
-        <v>208.61</v>
+        <v>214.149</v>
       </c>
       <c r="F92">
-        <v>498.51</v>
+        <v>504.049</v>
       </c>
       <c r="G92">
         <v>17.6</v>
@@ -8819,28 +8819,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M92">
-        <v>37.787058</v>
+        <v>38.2069142</v>
       </c>
       <c r="N92">
-        <v>48.97960866666668</v>
+        <v>48.55975246666668</v>
       </c>
       <c r="O92">
-        <v>12.21551440146667</v>
+        <v>12.11080226518667</v>
       </c>
       <c r="P92">
-        <v>36.76409426520001</v>
+        <v>36.44895020148001</v>
       </c>
       <c r="Q92">
-        <v>45.16409426520001</v>
+        <v>44.84895020148001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3426967413511898</v>
+        <v>0.3746244152670281</v>
       </c>
       <c r="T92">
-        <v>6.85673767554711</v>
+        <v>7.594097350277786</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.296200637442234</v>
+        <v>2.270967663404408</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08549108417403252</v>
+        <v>0.08550656221294609</v>
       </c>
       <c r="C93">
-        <v>-39.28279899979447</v>
+        <v>-44.97173158987465</v>
       </c>
       <c r="D93">
-        <v>447.1662010002055</v>
+        <v>447.0162684101253</v>
       </c>
       <c r="E93">
-        <v>214.149</v>
+        <v>219.688</v>
       </c>
       <c r="F93">
-        <v>504.049</v>
+        <v>509.588</v>
       </c>
       <c r="G93">
         <v>17.6</v>
@@ -8901,28 +8901,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M93">
-        <v>38.2069142</v>
+        <v>38.62677040000001</v>
       </c>
       <c r="N93">
-        <v>48.55975246666668</v>
+        <v>48.13989626666667</v>
       </c>
       <c r="O93">
-        <v>12.11080226518667</v>
+        <v>12.00609012890667</v>
       </c>
       <c r="P93">
-        <v>36.44895020148001</v>
+        <v>36.13380613776</v>
       </c>
       <c r="Q93">
-        <v>44.84895020148001</v>
+        <v>44.53380613776</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3746244152670281</v>
+        <v>0.4145340076618261</v>
       </c>
       <c r="T93">
-        <v>7.594097350277786</v>
+        <v>8.515796943691136</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.270967663404408</v>
+        <v>2.246283232280446</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08550656221294609</v>
+        <v>0.08552204025185961</v>
       </c>
       <c r="C94">
-        <v>-44.97173158987465</v>
+        <v>-50.66056367035998</v>
       </c>
       <c r="D94">
-        <v>447.0162684101253</v>
+        <v>446.86643632964</v>
       </c>
       <c r="E94">
-        <v>219.688</v>
+        <v>225.227</v>
       </c>
       <c r="F94">
-        <v>509.588</v>
+        <v>515.127</v>
       </c>
       <c r="G94">
         <v>17.6</v>
@@ -8983,28 +8983,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M94">
-        <v>38.62677040000001</v>
+        <v>39.0466266</v>
       </c>
       <c r="N94">
-        <v>48.13989626666667</v>
+        <v>47.72004006666668</v>
       </c>
       <c r="O94">
-        <v>12.00609012890667</v>
+        <v>11.90137799262667</v>
       </c>
       <c r="P94">
-        <v>36.13380613776</v>
+        <v>35.81866207404001</v>
       </c>
       <c r="Q94">
-        <v>44.53380613776</v>
+        <v>44.21866207404001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4145340076618261</v>
+        <v>0.4658463407408519</v>
       </c>
       <c r="T94">
-        <v>8.515796943691136</v>
+        <v>9.700839278079723</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.246283232280446</v>
+        <v>2.222129649137647</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08552204025185961</v>
+        <v>0.08553751829077316</v>
       </c>
       <c r="C95">
-        <v>-50.66056367035998</v>
+        <v>-56.34929534228473</v>
       </c>
       <c r="D95">
-        <v>446.86643632964</v>
+        <v>446.7167046577153</v>
       </c>
       <c r="E95">
-        <v>225.227</v>
+        <v>230.7660000000001</v>
       </c>
       <c r="F95">
-        <v>515.127</v>
+        <v>520.6660000000001</v>
       </c>
       <c r="G95">
         <v>17.6</v>
@@ -9065,28 +9065,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M95">
-        <v>39.0466266</v>
+        <v>39.46648280000001</v>
       </c>
       <c r="N95">
-        <v>47.72004006666668</v>
+        <v>47.30018386666667</v>
       </c>
       <c r="O95">
-        <v>11.90137799262667</v>
+        <v>11.79666585634667</v>
       </c>
       <c r="P95">
-        <v>35.81866207404001</v>
+        <v>35.50351801032</v>
       </c>
       <c r="Q95">
-        <v>44.21866207404001</v>
+        <v>43.90351801032</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4658463407408519</v>
+        <v>0.5342627848462198</v>
       </c>
       <c r="T95">
-        <v>9.700839278079723</v>
+        <v>11.28089572393118</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.222129649137647</v>
+        <v>2.19848997201916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08553751829077316</v>
+        <v>0.08555299632968671</v>
       </c>
       <c r="C96">
-        <v>-56.34929534228473</v>
+        <v>-62.03792670654639</v>
       </c>
       <c r="D96">
-        <v>446.7167046577153</v>
+        <v>446.5670732934536</v>
       </c>
       <c r="E96">
-        <v>230.7660000000001</v>
+        <v>236.3050000000001</v>
       </c>
       <c r="F96">
-        <v>520.6660000000001</v>
+        <v>526.205</v>
       </c>
       <c r="G96">
         <v>17.6</v>
@@ -9147,28 +9147,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M96">
-        <v>39.46648280000001</v>
+        <v>39.88633900000001</v>
       </c>
       <c r="N96">
-        <v>47.30018386666667</v>
+        <v>46.88032766666667</v>
       </c>
       <c r="O96">
-        <v>11.79666585634667</v>
+        <v>11.69195372006667</v>
       </c>
       <c r="P96">
-        <v>35.50351801032</v>
+        <v>35.1883739466</v>
       </c>
       <c r="Q96">
-        <v>43.90351801032</v>
+        <v>43.5883739466</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5342627848462198</v>
+        <v>0.6300458065937351</v>
       </c>
       <c r="T96">
-        <v>11.28089572393118</v>
+        <v>13.49297474812322</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.19848997201916</v>
+        <v>2.175347972313695</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08555299632968671</v>
+        <v>0.08556847436860027</v>
       </c>
       <c r="C97">
-        <v>-62.03792670654639</v>
+        <v>-67.72645786390774</v>
       </c>
       <c r="D97">
-        <v>446.5670732934536</v>
+        <v>446.4175421360923</v>
       </c>
       <c r="E97">
-        <v>236.3050000000001</v>
+        <v>241.8440000000001</v>
       </c>
       <c r="F97">
-        <v>526.205</v>
+        <v>531.744</v>
       </c>
       <c r="G97">
         <v>17.6</v>
@@ -9229,28 +9229,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M97">
-        <v>39.88633900000001</v>
+        <v>40.3061952</v>
       </c>
       <c r="N97">
-        <v>46.88032766666667</v>
+        <v>46.46047146666668</v>
       </c>
       <c r="O97">
-        <v>11.69195372006667</v>
+        <v>11.58724158378667</v>
       </c>
       <c r="P97">
-        <v>35.1883739466</v>
+        <v>34.87322988288</v>
       </c>
       <c r="Q97">
-        <v>43.5883739466</v>
+        <v>43.27322988288</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6300458065937351</v>
+        <v>0.7737203392150078</v>
       </c>
       <c r="T97">
-        <v>13.49297474812322</v>
+        <v>16.81109328441127</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.175347972313695</v>
+        <v>2.152688097602094</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08556847436860025</v>
+        <v>0.08558395240751382</v>
       </c>
       <c r="C98">
-        <v>-67.72645786390746</v>
+        <v>-73.41488891499682</v>
       </c>
       <c r="D98">
-        <v>446.4175421360924</v>
+        <v>446.2681110850032</v>
       </c>
       <c r="E98">
-        <v>241.8439999999999</v>
+        <v>247.383</v>
       </c>
       <c r="F98">
-        <v>531.7439999999999</v>
+        <v>537.283</v>
       </c>
       <c r="G98">
         <v>17.6</v>
@@ -9311,28 +9311,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M98">
-        <v>40.3061952</v>
+        <v>40.7260514</v>
       </c>
       <c r="N98">
-        <v>46.46047146666668</v>
+        <v>46.04061526666668</v>
       </c>
       <c r="O98">
-        <v>11.58724158378667</v>
+        <v>11.48252944750667</v>
       </c>
       <c r="P98">
-        <v>34.87322988288001</v>
+        <v>34.55808581916001</v>
       </c>
       <c r="Q98">
-        <v>43.27322988288001</v>
+        <v>42.95808581916</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7737203392150058</v>
+        <v>1.013177893583793</v>
       </c>
       <c r="T98">
-        <v>16.81109328441122</v>
+        <v>22.3412908448913</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.152688097602095</v>
+        <v>2.130495436802073</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08558395240751382</v>
+        <v>0.08559943044642737</v>
       </c>
       <c r="C99">
-        <v>-73.41488891499682</v>
+        <v>-79.10321996030683</v>
       </c>
       <c r="D99">
-        <v>446.2681110850032</v>
+        <v>446.1187800396931</v>
       </c>
       <c r="E99">
-        <v>247.383</v>
+        <v>252.922</v>
       </c>
       <c r="F99">
-        <v>537.283</v>
+        <v>542.822</v>
       </c>
       <c r="G99">
         <v>17.6</v>
@@ -9393,28 +9393,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M99">
-        <v>40.7260514</v>
+        <v>41.1459076</v>
       </c>
       <c r="N99">
-        <v>46.04061526666668</v>
+        <v>45.62075906666668</v>
       </c>
       <c r="O99">
-        <v>11.48252944750667</v>
+        <v>11.37781731122667</v>
       </c>
       <c r="P99">
-        <v>34.55808581916001</v>
+        <v>34.24294175544001</v>
       </c>
       <c r="Q99">
-        <v>42.95808581916</v>
+        <v>42.64294175544001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.013177893583793</v>
+        <v>1.492093002321367</v>
       </c>
       <c r="T99">
-        <v>22.3412908448913</v>
+        <v>33.40168596585143</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.130495436802073</v>
+        <v>2.10875568744695</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08559943044642737</v>
+        <v>0.0856149084853409</v>
       </c>
       <c r="C100">
-        <v>-79.10321996030683</v>
+        <v>-84.79145110019635</v>
       </c>
       <c r="D100">
-        <v>446.1187800396931</v>
+        <v>445.9695488998036</v>
       </c>
       <c r="E100">
-        <v>252.922</v>
+        <v>258.461</v>
       </c>
       <c r="F100">
-        <v>542.822</v>
+        <v>548.361</v>
       </c>
       <c r="G100">
         <v>17.6</v>
@@ -9475,28 +9475,28 @@
         <v>86.76666666666668</v>
       </c>
       <c r="M100">
-        <v>41.1459076</v>
+        <v>41.5657638</v>
       </c>
       <c r="N100">
-        <v>45.62075906666668</v>
+        <v>45.20090286666668</v>
       </c>
       <c r="O100">
-        <v>11.37781731122667</v>
+        <v>11.27310517494667</v>
       </c>
       <c r="P100">
-        <v>34.24294175544001</v>
+        <v>33.92779769172001</v>
       </c>
       <c r="Q100">
-        <v>42.64294175544001</v>
+        <v>42.32779769172001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.492093002321367</v>
+        <v>2.928838328534088</v>
       </c>
       <c r="T100">
-        <v>33.40168596585143</v>
+        <v>66.58287132873184</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.10875568744695</v>
+        <v>2.087455124947486</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0856149084853409</v>
-      </c>
-      <c r="C101">
-        <v>-84.79145110019635</v>
-      </c>
-      <c r="D101">
-        <v>445.9695488998036</v>
-      </c>
-      <c r="E101">
-        <v>258.461</v>
-      </c>
-      <c r="F101">
-        <v>548.361</v>
-      </c>
-      <c r="G101">
-        <v>17.6</v>
-      </c>
-      <c r="H101">
-        <v>264</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>95.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>8.399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>86.76666666666668</v>
-      </c>
-      <c r="M101">
-        <v>41.5657638</v>
-      </c>
-      <c r="N101">
-        <v>45.20090286666668</v>
-      </c>
-      <c r="O101">
-        <v>11.27310517494667</v>
-      </c>
-      <c r="P101">
-        <v>33.92779769172001</v>
-      </c>
-      <c r="Q101">
-        <v>42.32779769172001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.928838328534088</v>
-      </c>
-      <c r="T101">
-        <v>66.58287132873184</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.05689548</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.087455124947486</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
